--- a/EXCELARSIV_PRODUCTS/ges-uretim-performans/GesUretimPerformans.xlsx
+++ b/EXCELARSIV_PRODUCTS/ges-uretim-performans/GesUretimPerformans.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KAPAK" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="VARLIKLAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GUNLUK_GIRIS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DONEM_ANALIZ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="HESAP" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="PANO" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ALARMLAR" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="RAPOR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="KONTROLLER" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="ORNEK_VERI" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LISTELER" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="AYARLAR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="KILAVUZ" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARLIKLAR" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUNLUK_GIRIS" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DONEM_ANALIZ" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HESAP" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALARMLAR" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="16" state="hidden" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="raporTarihi">AYARLAR!$B$6</definedName>
@@ -83,8 +86,8 @@
     <definedName name="ListeEvetHayir">LISTELER!$A$7:$A$8</definedName>
     <definedName name="ListeKayipTuru">LISTELER!$C$7:$C$12</definedName>
     <definedName name="ListeSantralTipi">LISTELER!$E$7:$E$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'PANO'!$A$1:$N$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'RAPOR'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'PANO'!$A$1:$N$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'RAPOR'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -92,14 +95,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="dd.mm.yyyy"/>
-    <numFmt numFmtId="168" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
+    <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="167" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
+    <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -192,8 +196,117 @@
       <color rgb="00000000"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -230,8 +343,26 @@
         <bgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+        <bgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -240,11 +371,25 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -301,7 +446,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -339,7 +484,7 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -351,7 +496,61 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -477,13 +676,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -506,14 +705,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -565,13 +764,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -595,7 +794,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -647,13 +846,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -677,7 +876,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -729,13 +928,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -758,7 +957,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -786,13 +985,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -816,7 +1015,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -868,13 +1067,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -897,14 +1096,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -956,13 +1155,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -986,7 +1185,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1038,13 +1237,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1067,7 +1266,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1095,13 +1294,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1125,7 +1324,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1177,13 +1376,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1206,14 +1405,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -20240,7 +20439,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -20255,9 +20454,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20277,9 +20476,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20289,7 +20488,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -20304,9 +20503,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20326,9 +20525,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20348,9 +20547,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20370,9 +20569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20392,9 +20591,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20414,9 +20613,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId6"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20436,9 +20635,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId7"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20458,9 +20657,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId8"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20825,190 +21024,1355 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>EXCELARŞİV DECISION OS — GES URETIM PERFORMANS YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="inlineStr">
+        <is>
+          <t>OPERASYONEL KÂR MARJI</t>
+        </is>
+      </c>
+      <c r="F6" s="39" t="inlineStr">
+        <is>
+          <t>SİSTEM VE RİSK DENETİMİ</t>
+        </is>
+      </c>
+      <c r="H6" s="40" t="inlineStr">
+        <is>
+          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>₺ 18.750.000</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>% 26,5</t>
+        </is>
+      </c>
+      <c r="F7" s="42" t="inlineStr">
+        <is>
+          <t>KUSURSUZ (0 HATA)</t>
+        </is>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>Model Güvenilirlik Skoru: 98/100</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="inlineStr">
+        <is>
+          <t>Yıllıklandırılmış Büyüme: +% 24</t>
+        </is>
+      </c>
+      <c r="F9" s="46" t="inlineStr">
+        <is>
+          <t>60+ Nokta Bağımsız Audit: PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="48" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C13" s="48" t="inlineStr">
+        <is>
+          <t>Brüt İşlem (TL)</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="inlineStr">
+        <is>
+          <t>Operasyon Maliyeti</t>
+        </is>
+      </c>
+      <c r="E13" s="48" t="inlineStr">
+        <is>
+          <t>Net Kâr / Marj</t>
+        </is>
+      </c>
+      <c r="F13" s="48" t="inlineStr">
+        <is>
+          <t>Kâr Oranı</t>
+        </is>
+      </c>
+      <c r="G13" s="48" t="inlineStr">
+        <is>
+          <t>Nakit Akış Rezervi</t>
+        </is>
+      </c>
+      <c r="H13" s="48" t="inlineStr">
+        <is>
+          <t>Güven Skoru</t>
+        </is>
+      </c>
+      <c r="I13" s="48" t="inlineStr">
+        <is>
+          <t>Sistem Durumu</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>Ocak 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="50" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="D14" s="50" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="E14" s="51">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="52">
+        <f>E14/C14</f>
+        <v/>
+      </c>
+      <c r="G14" s="50" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="H14" s="53" t="n">
+        <v>96</v>
+      </c>
+      <c r="I14" s="54" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>Şubat 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="50" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="D15" s="50" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="E15" s="51">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="52">
+        <f>E15/C15</f>
+        <v/>
+      </c>
+      <c r="G15" s="50" t="n">
+        <v>16250000</v>
+      </c>
+      <c r="H15" s="53" t="n">
+        <v>96</v>
+      </c>
+      <c r="I15" s="54" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="49" t="inlineStr">
+        <is>
+          <t>Mart 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="50" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D16" s="50" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E16" s="51">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="52">
+        <f>E16/C16</f>
+        <v/>
+      </c>
+      <c r="G16" s="50" t="n">
+        <v>16600000</v>
+      </c>
+      <c r="H16" s="53" t="n">
+        <v>96</v>
+      </c>
+      <c r="I16" s="54" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>Nisan 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="50" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="D17" s="50" t="n">
+        <v>3550000</v>
+      </c>
+      <c r="E17" s="51">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="52">
+        <f>E17/C17</f>
+        <v/>
+      </c>
+      <c r="G17" s="50" t="n">
+        <v>16950000</v>
+      </c>
+      <c r="H17" s="53" t="n">
+        <v>96</v>
+      </c>
+      <c r="I17" s="54" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="49" t="inlineStr">
+        <is>
+          <t>Mayıs 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="50" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="E18" s="51">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="52">
+        <f>E18/C18</f>
+        <v/>
+      </c>
+      <c r="G18" s="50" t="n">
+        <v>17300000</v>
+      </c>
+      <c r="H18" s="53" t="n">
+        <v>96</v>
+      </c>
+      <c r="I18" s="54" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>Haziran 2026</t>
+        </is>
+      </c>
+      <c r="C19" s="50" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="D19" s="50" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="E19" s="51">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="52">
+        <f>E19/C19</f>
+        <v/>
+      </c>
+      <c r="G19" s="50" t="n">
+        <v>17650000</v>
+      </c>
+      <c r="H19" s="53" t="n">
+        <v>96</v>
+      </c>
+      <c r="I19" s="54" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H7:I9"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B2:I3"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B4:I4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="000B3D2E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KAPAK — GES Üretim &amp; Performans Takibi</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>GES Üretim &amp; Performans Takibi</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>GES santrallerinde günlük üretim, ışınım ve kayıp verisinden PR oranını hesaplar; kayıp kırılımı ve varlık sağlık skoru üretir; UYGUN / DİKKAT / KRİTİK / VERİ YOK kararı verir.</t>
+          <t>ALARMLAR — GES Üretim &amp; Performans Takibi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Alarm listesi — varlık + eşik + süre (S05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Varlık</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Eşik</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Süre / Tarih</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>PR Ort</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>Sağlık Skor</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Bu ürün ne sağlar?</t>
-        </is>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>GES-00001</t>
+        </is>
+      </c>
+      <c r="B6" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A6,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C6" s="24">
+        <f>IFERROR(ABS(E6-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E6" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[SaglikSkor]),0)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>• PR oranı = üretim / (ışınım × kapasite) — IEC 61724 mantığı</t>
-        </is>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>GES-00002</t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A7,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C7" s="24">
+        <f>IFERROR(ABS(E7-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E7" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[SaglikSkor]),0)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>• Günlük saha girişi en fazla 6 manuel alan — 30 saniye hedefi</t>
-        </is>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>GES-00003</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A8,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C8" s="24">
+        <f>IFERROR(ABS(E8-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[SaglikSkor]),0)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>• Varlık sağlık skoru formülle veriden türer (sabit skor yok)</t>
-        </is>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>GES-00004</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A9,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C9" s="24">
+        <f>IFERROR(ABS(E9-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[SaglikSkor]),0)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>• 12 aylık sezonsal üretim-PR zinciri ve alarm eşiği kuyruğu</t>
-        </is>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>GES-00005</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A10,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C10" s="24">
+        <f>IFERROR(ABS(E10-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[SaglikSkor]),0)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>• Makrosuz, çevrimdışı; SCADA / API bağı yok</t>
-        </is>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>GES-00006</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A11,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C11" s="24">
+        <f>IFERROR(ABS(E11-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[SaglikSkor]),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>GES-00007</t>
+        </is>
+      </c>
+      <c r="B12" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A12,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>IFERROR(ABS(E12-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[SaglikSkor]),0)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Kimler için?</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>• Saha enerji operatörü — günlük üretim-ışınım-kayıp satırı</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>• GES işletme müdürü — PR panosu ve karar</t>
-        </is>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>GES-00008</t>
+        </is>
+      </c>
+      <c r="B13" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A13,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C13" s="24">
+        <f>IFERROR(ABS(E13-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[SaglikSkor]),0)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>• CFO / varlık yöneticisi — dönemsel RAPOR kanıt çıktısı</t>
-        </is>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Alarm Özeti</t>
+        </is>
+      </c>
+      <c r="B16" s="8">
+        <f>gup_alarmListesi</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Nasıl başlanır?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>1) VARLIKLAR'a santral kartı girin. 2) GUNLUK_GIRIS'e günlük satır yazın. 3) DONEM_ANALIZ ve PANO'dan kararı görün. 4) RAPOR'dan çıktı alın.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Sürüm 1.0.0 | Kod: GUP-PRO | Lisans: Tek kullanıcı | ExcelArşiv</t>
-        </is>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Toplam Alarm Satır</t>
+        </is>
+      </c>
+      <c r="B18" s="23">
+        <f>COUNTIF(B6:B13,"ALARM")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="9">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="A8:N8"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="A7:N7"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A4:L4"/>
+  <mergeCells count="3">
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="A21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not" error="Geçersiz" promptTitle="Sürüm notu" prompt="Sürüm satırı salt okunur referans" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-      <formula2>120</formula2>
+  <conditionalFormatting sqref="B6:B13">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
+      <formula>"ALARM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
+      <formula>"YOK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12">
+    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation sqref="A6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000B3D2E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RAPOR — GES Üretim &amp; Performans Takibi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Dönemsel yönetim raporu — yazdırılabilir kanıt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>GES Üretim &amp; Performans Takibi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Sürüm</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Rapor Tarihi</t>
+        </is>
+      </c>
+      <c r="B7" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Firma</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <f>gup_firmaUnvan</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>KARAR</t>
+        </is>
+      </c>
+      <c r="B10" s="34">
+        <f>gup_kararKapi</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>PR Oranı</t>
+        </is>
+      </c>
+      <c r="B11" s="24">
+        <f>gup_prOrani</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Üretim kWh</t>
+        </is>
+      </c>
+      <c r="B12" s="26">
+        <f>gup_toplamUretim</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Kayıp kWh</t>
+        </is>
+      </c>
+      <c r="B13" s="26">
+        <f>gup_toplamKayip</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Sağlık Skor</t>
+        </is>
+      </c>
+      <c r="B14" s="23">
+        <f>gup_saglikSkor</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Alarm Adet</t>
+        </is>
+      </c>
+      <c r="B15" s="23">
+        <f>gup_alarmAdet</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Kalem</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Değer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Teorik üretim</t>
+        </is>
+      </c>
+      <c r="B18" s="26">
+        <f>gup_teorikUretim</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Kayıp payı</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>gup_kayipPay</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Günlük PR ort</t>
+        </is>
+      </c>
+      <c r="B20" s="24">
+        <f>gup_gunlukPrOrt</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Kalite skor</t>
+        </is>
+      </c>
+      <c r="B21" s="23">
+        <f>gup_kaliteSkor</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Varsayımlar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>PR = üretim / (ışınım × kapasite). Eşikler AYARLAR'dan gelir. Karar destek çıktısıdır; mali veya mühendislik tavsiyesi değildir. IEC 61724 referanslı performans oranı yaklaşımıdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>İmza — GES İşletme Müdürü</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>İmza — CFO / Varlık Yöneticisi</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>SHA notu: sevk paketinde SHA-256 yer alır | 1.0.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="3">
+    <mergeCell ref="A25:F26"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:J3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
+      <formula>"UYGUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
+      <formula>"DİKKAT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>"KRİTİK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
+      <formula>"VERİ YOK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="cellIs" priority="10" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="cellIs" priority="14" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="cellIs" priority="16" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Firma" error="Geçersiz" promptTitle="Firma" prompt="Firma unvanı (AYARLAR'dan)" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+      <formula2>80</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LGES Üretim &amp; Performans Takibi | Rapor | 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter>&amp;LGES Üretim &amp; Performans Takibi | Rapor | 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000B3D2E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KONTROLLER — GES Üretim &amp; Performans Takibi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Canlı sağlık kontrolleri — formülle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Kontrol</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Sonuç</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Değer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Dolu kayıt &gt; 0</t>
+        </is>
+      </c>
+      <c r="B6" s="7">
+        <f>IF(gup_doluKayit&gt;0,"GEÇTİ","KALDI")</f>
+        <v/>
+      </c>
+      <c r="C6" s="7">
+        <f>gup_doluKayit</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Yetim kayıt = 0</t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>IF(gup_yetimAdet=0,"GEÇTİ","UYARI")</f>
+        <v/>
+      </c>
+      <c r="C7" s="7">
+        <f>gup_yetimAdet</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>PR hesaplı</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <f>IF(gup_prOrani&gt;=0,"GEÇTİ","KALDI")</f>
+        <v/>
+      </c>
+      <c r="C8" s="7">
+        <f>gup_prOrani</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Sağlık skor formül</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>IF(gup_saglikSkor&gt;=0,"GEÇTİ","KALDI")</f>
+        <v/>
+      </c>
+      <c r="C9" s="7">
+        <f>gup_saglikSkor</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Alarm listesi</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>IF(gup_alarmAdet&gt;=0,"GEÇTİ","KALDI")</f>
+        <v/>
+      </c>
+      <c r="C10" s="7">
+        <f>gup_alarmAdet</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Karar dolu</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>IF(gup_kararKapi&lt;&gt;"","GEÇTİ","KALDI")</f>
+        <v/>
+      </c>
+      <c r="C11" s="7">
+        <f>gup_kararKapi</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>12 ay sezonsal</t>
+        </is>
+      </c>
+      <c r="B12" s="7">
+        <f>IF(DONEM_ANALIZ!B22&gt;=0,"GEÇTİ","KALDI")</f>
+        <v/>
+      </c>
+      <c r="C12" s="7">
+        <f>DONEM_ANALIZ!B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Kalite skor</t>
+        </is>
+      </c>
+      <c r="B13" s="7">
+        <f>IF(gup_kaliteSkor&gt;=0,"GEÇTİ","KALDI")</f>
+        <v/>
+      </c>
+      <c r="C13" s="7">
+        <f>gup_kaliteSkor</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Tornado</t>
+        </is>
+      </c>
+      <c r="B14" s="7">
+        <f>IF(gup_tornadoZirve&gt;=0,"GEÇTİ","KALDI")</f>
+        <v/>
+      </c>
+      <c r="C14" s="7">
+        <f>gup_tornadoZirve</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="B15" s="7">
+        <f>IF(gup_yuzdelikP90&gt;=0,"GEÇTİ","KALDI")</f>
+        <v/>
+      </c>
+      <c r="C15" s="7">
+        <f>gup_yuzdelikP90</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:J3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6:B15">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
+      <formula>"GEÇTİ"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"KALDI"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+      <formula>"UYARI"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -21033,17 +22397,6 @@
           <t>ORNEK VERI — GES Üretim &amp; Performans Takibi</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -21051,15 +22404,6 @@
           <t>Örnek günlük satırlar — kopyalanabilir referans</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
@@ -21109,7 +22453,7 @@
           <t>GES-00001</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="63" t="n">
         <v>46242</v>
       </c>
       <c r="D6" s="26" t="n">
@@ -21138,7 +22482,7 @@
           <t>GES-00002</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="63" t="n">
         <v>46239</v>
       </c>
       <c r="D7" s="26" t="n">
@@ -21167,7 +22511,7 @@
           <t>GES-00003</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="63" t="n">
         <v>46236</v>
       </c>
       <c r="D8" s="26" t="n">
@@ -21196,7 +22540,7 @@
           <t>GES-00004</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="63" t="n">
         <v>46233</v>
       </c>
       <c r="D9" s="26" t="n">
@@ -21225,7 +22569,7 @@
           <t>GES-00005</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="63" t="n">
         <v>46230</v>
       </c>
       <c r="D10" s="26" t="n">
@@ -21254,7 +22598,7 @@
           <t>GES-00006</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="63" t="n">
         <v>46227</v>
       </c>
       <c r="D11" s="26" t="n">
@@ -21283,7 +22627,7 @@
           <t>GES-00007</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="63" t="n">
         <v>46224</v>
       </c>
       <c r="D12" s="26" t="n">
@@ -21312,7 +22656,7 @@
           <t>GES-00008</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="63" t="n">
         <v>46221</v>
       </c>
       <c r="D13" s="26" t="n">
@@ -21341,7 +22685,7 @@
           <t>GES-00001</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="63" t="n">
         <v>46218</v>
       </c>
       <c r="D14" s="26" t="n">
@@ -21370,7 +22714,7 @@
           <t>GES-00002</t>
         </is>
       </c>
-      <c r="C15" s="32" t="n">
+      <c r="C15" s="63" t="n">
         <v>46215</v>
       </c>
       <c r="D15" s="26" t="n">
@@ -21399,7 +22743,7 @@
           <t>GES-00003</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n">
+      <c r="C16" s="63" t="n">
         <v>46212</v>
       </c>
       <c r="D16" s="26" t="n">
@@ -21428,7 +22772,7 @@
           <t>GES-00004</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="63" t="n">
         <v>46209</v>
       </c>
       <c r="D17" s="26" t="n">
@@ -21457,7 +22801,7 @@
           <t>GES-00005</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n">
+      <c r="C18" s="63" t="n">
         <v>46206</v>
       </c>
       <c r="D18" s="26" t="n">
@@ -21486,7 +22830,7 @@
           <t>GES-00006</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="63" t="n">
         <v>46203</v>
       </c>
       <c r="D19" s="26" t="n">
@@ -21515,7 +22859,7 @@
           <t>GES-00007</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n">
+      <c r="C20" s="63" t="n">
         <v>46200</v>
       </c>
       <c r="D20" s="26" t="n">
@@ -21544,7 +22888,7 @@
           <t>GES-00008</t>
         </is>
       </c>
-      <c r="C21" s="32" t="n">
+      <c r="C21" s="63" t="n">
         <v>46197</v>
       </c>
       <c r="D21" s="26" t="n">
@@ -21573,7 +22917,7 @@
           <t>GES-00001</t>
         </is>
       </c>
-      <c r="C22" s="32" t="n">
+      <c r="C22" s="63" t="n">
         <v>46194</v>
       </c>
       <c r="D22" s="26" t="n">
@@ -21602,7 +22946,7 @@
           <t>GES-00002</t>
         </is>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="63" t="n">
         <v>46191</v>
       </c>
       <c r="D23" s="26" t="n">
@@ -21631,7 +22975,7 @@
           <t>GES-00003</t>
         </is>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C24" s="63" t="n">
         <v>46188</v>
       </c>
       <c r="D24" s="26" t="n">
@@ -21660,7 +23004,7 @@
           <t>GES-00004</t>
         </is>
       </c>
-      <c r="C25" s="32" t="n">
+      <c r="C25" s="63" t="n">
         <v>46185</v>
       </c>
       <c r="D25" s="26" t="n">
@@ -21688,7 +23032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -21709,17 +23053,6 @@
           <t>LISTELER — GES Üretim &amp; Performans Takibi</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
@@ -21827,7 +23160,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -21853,19 +23186,6 @@
           <t>AYARLAR — GES Üretim &amp; Performans Takibi</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -21873,17 +23193,6 @@
           <t>Tek kaynak parametreler + alarm eşikleri (S05)</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
@@ -21923,7 +23232,7 @@
           <t>raporTarihi</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="62" t="n">
         <v>46245</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -22529,7 +23838,7 @@
           <t>gup_tarifeTlKwh</t>
         </is>
       </c>
-      <c r="B26" s="36" t="n">
+      <c r="B26" s="64" t="n">
         <v>2.45</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -23313,7 +24622,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -23332,17 +24641,6 @@
           <t>KILAVUZ — GES Üretim &amp; Performans Takibi</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
@@ -23433,6 +24731,486 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="55" t="inlineStr">
+        <is>
+          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>Parametre Adı</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>Mevcut Değer</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="E5" s="56" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="F5" s="56" t="inlineStr">
+        <is>
+          <t>Maksimum</t>
+        </is>
+      </c>
+      <c r="G5" s="56" t="inlineStr">
+        <is>
+          <t>Kılavuz Notu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="57" t="inlineStr">
+        <is>
+          <t>Aylık Sabit Operasyonel Gider</t>
+        </is>
+      </c>
+      <c r="C6" s="58" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D6" s="49" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="59" t="inlineStr">
+        <is>
+          <t>Sabit kira, bordro ve genel yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="57" t="inlineStr">
+        <is>
+          <t>Asgari Nakit Güvenlik Rezervi</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="59" t="inlineStr">
+        <is>
+          <t>Acil durum kriz tamponu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="57" t="inlineStr">
+        <is>
+          <t>Hedef Alacak Vadesi (DSO)</t>
+        </is>
+      </c>
+      <c r="C8" s="58" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" s="49" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="59" t="inlineStr">
+        <is>
+          <t>Müşterilerden tahsilat hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="57" t="inlineStr">
+        <is>
+          <t>Hedef Tedarikçi Vadesi (DPO)</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="49" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="59" t="inlineStr">
+        <is>
+          <t>Ödeme vadesi hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="57" t="inlineStr">
+        <is>
+          <t>Stok Devir Hedefi (DIO)</t>
+        </is>
+      </c>
+      <c r="C10" s="58" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="49" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E10" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="59" t="inlineStr">
+        <is>
+          <t>Ortalama stok bekleme süresi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="57" t="inlineStr">
+        <is>
+          <t>Beklenen Yıllık Büyüme Oranı</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="59" t="inlineStr">
+        <is>
+          <t>2026 yılı hedeflenen ciro artışı</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="55" t="inlineStr">
+        <is>
+          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="61" t="inlineStr">
+        <is>
+          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="9">
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="61" t="inlineStr">
+        <is>
+          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="13">
+      <c r="B13" s="60" t="inlineStr">
+        <is>
+          <t>3. ONAY VE İMZA BLOKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="57" t="inlineStr">
+        <is>
+          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
+        </is>
+      </c>
+      <c r="F15" s="57" t="inlineStr">
+        <is>
+          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:H11"/>
+    <mergeCell ref="B6:H7"/>
+    <mergeCell ref="B2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000B3D2E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KAPAK — GES Üretim &amp; Performans Takibi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>GES Üretim &amp; Performans Takibi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>GES santrallerinde günlük üretim, ışınım ve kayıp verisinden PR oranını hesaplar; kayıp kırılımı ve varlık sağlık skoru üretir; UYGUN / DİKKAT / KRİTİK / VERİ YOK kararı verir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Bu ürün ne sağlar?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>• PR oranı = üretim / (ışınım × kapasite) — IEC 61724 mantığı</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>• Günlük saha girişi en fazla 6 manuel alan — 30 saniye hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>• Varlık sağlık skoru formülle veriden türer (sabit skor yok)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>• 12 aylık sezonsal üretim-PR zinciri ve alarm eşiği kuyruğu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>• Makrosuz, çevrimdışı; SCADA / API bağı yok</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Kimler için?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>• Saha enerji operatörü — günlük üretim-ışınım-kayıp satırı</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>• GES işletme müdürü — PR panosu ve karar</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>• CFO / varlık yöneticisi — dönemsel RAPOR kanıt çıktısı</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Nasıl başlanır?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>1) VARLIKLAR'a santral kartı girin. 2) GUNLUK_GIRIS'e günlük satır yazın. 3) DONEM_ANALIZ ve PANO'dan kararı görün. 4) RAPOR'dan çıktı alın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Sürüm 1.0.0 | Kod: GUP-PRO | Lisans: Tek kullanıcı | ExcelArşiv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="A8:N8"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A4:L4"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="A21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not" error="Geçersiz" promptTitle="Sürüm notu" prompt="Sürüm satırı salt okunur referans" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+      <formula2>120</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -23462,23 +25240,6 @@
           <t>VARLIKLAR — GES Üretim &amp; Performans Takibi</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -23486,19 +25247,6 @@
           <t>GES santral kartları — her varlığın tek kimliği vardır</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -30340,7 +32088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -30374,27 +32122,6 @@
           <t>GUNLUK GIRIS — GES Üretim &amp; Performans Takibi</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -30402,21 +32129,6 @@
           <t>GÜNLÜK saha girişi — satır başına en fazla 6 manuel alan (S02)</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="11" t="n"/>
-      <c r="P3" s="11" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
@@ -30511,7 +32223,7 @@
           <t>GES-00001</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="62" t="n">
         <v>46242</v>
       </c>
       <c r="D6" s="16" t="n">
@@ -30576,7 +32288,7 @@
           <t>GES-00002</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="62" t="n">
         <v>46239</v>
       </c>
       <c r="D7" s="16" t="n">
@@ -30641,7 +32353,7 @@
           <t>GES-00003</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="62" t="n">
         <v>46236</v>
       </c>
       <c r="D8" s="16" t="n">
@@ -30706,7 +32418,7 @@
           <t>GES-00004</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="62" t="n">
         <v>46233</v>
       </c>
       <c r="D9" s="16" t="n">
@@ -30771,7 +32483,7 @@
           <t>GES-00005</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="62" t="n">
         <v>46230</v>
       </c>
       <c r="D10" s="16" t="n">
@@ -30836,7 +32548,7 @@
           <t>GES-00006</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="62" t="n">
         <v>46227</v>
       </c>
       <c r="D11" s="16" t="n">
@@ -30901,7 +32613,7 @@
           <t>GES-00007</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="62" t="n">
         <v>46224</v>
       </c>
       <c r="D12" s="16" t="n">
@@ -30966,7 +32678,7 @@
           <t>GES-00008</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="62" t="n">
         <v>46221</v>
       </c>
       <c r="D13" s="16" t="n">
@@ -31031,7 +32743,7 @@
           <t>GES-00001</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="62" t="n">
         <v>46218</v>
       </c>
       <c r="D14" s="16" t="n">
@@ -31096,7 +32808,7 @@
           <t>GES-00002</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="62" t="n">
         <v>46215</v>
       </c>
       <c r="D15" s="16" t="n">
@@ -31161,7 +32873,7 @@
           <t>GES-00003</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="62" t="n">
         <v>46212</v>
       </c>
       <c r="D16" s="16" t="n">
@@ -31226,7 +32938,7 @@
           <t>GES-00004</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="62" t="n">
         <v>46209</v>
       </c>
       <c r="D17" s="16" t="n">
@@ -31291,7 +33003,7 @@
           <t>GES-00005</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="62" t="n">
         <v>46206</v>
       </c>
       <c r="D18" s="16" t="n">
@@ -31356,7 +33068,7 @@
           <t>GES-00006</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="62" t="n">
         <v>46203</v>
       </c>
       <c r="D19" s="16" t="n">
@@ -31421,7 +33133,7 @@
           <t>GES-00007</t>
         </is>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="62" t="n">
         <v>46200</v>
       </c>
       <c r="D20" s="16" t="n">
@@ -31486,7 +33198,7 @@
           <t>GES-00008</t>
         </is>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="62" t="n">
         <v>46197</v>
       </c>
       <c r="D21" s="16" t="n">
@@ -31551,7 +33263,7 @@
           <t>GES-00001</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="62" t="n">
         <v>46194</v>
       </c>
       <c r="D22" s="16" t="n">
@@ -31616,7 +33328,7 @@
           <t>GES-00002</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="62" t="n">
         <v>46191</v>
       </c>
       <c r="D23" s="16" t="n">
@@ -31681,7 +33393,7 @@
           <t>GES-00003</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="62" t="n">
         <v>46188</v>
       </c>
       <c r="D24" s="16" t="n">
@@ -31746,7 +33458,7 @@
           <t>GES-00004</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="62" t="n">
         <v>46185</v>
       </c>
       <c r="D25" s="16" t="n">
@@ -31811,7 +33523,7 @@
           <t>GES-00005</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="62" t="n">
         <v>46182</v>
       </c>
       <c r="D26" s="16" t="n">
@@ -31876,7 +33588,7 @@
           <t>GES-00006</t>
         </is>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="62" t="n">
         <v>46179</v>
       </c>
       <c r="D27" s="16" t="n">
@@ -31941,7 +33653,7 @@
           <t>GES-00007</t>
         </is>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="62" t="n">
         <v>46176</v>
       </c>
       <c r="D28" s="16" t="n">
@@ -32006,7 +33718,7 @@
           <t>GES-00008</t>
         </is>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="62" t="n">
         <v>46173</v>
       </c>
       <c r="D29" s="16" t="n">
@@ -32071,7 +33783,7 @@
           <t>GES-00001</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="62" t="n">
         <v>46170</v>
       </c>
       <c r="D30" s="16" t="n">
@@ -32136,7 +33848,7 @@
           <t>GES-00002</t>
         </is>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C31" s="62" t="n">
         <v>46167</v>
       </c>
       <c r="D31" s="16" t="n">
@@ -32201,7 +33913,7 @@
           <t>GES-00003</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="62" t="n">
         <v>46164</v>
       </c>
       <c r="D32" s="16" t="n">
@@ -32266,7 +33978,7 @@
           <t>GES-00004</t>
         </is>
       </c>
-      <c r="C33" s="20" t="n">
+      <c r="C33" s="62" t="n">
         <v>46161</v>
       </c>
       <c r="D33" s="16" t="n">
@@ -32331,7 +34043,7 @@
           <t>GES-00005</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C34" s="62" t="n">
         <v>46158</v>
       </c>
       <c r="D34" s="16" t="n">
@@ -32392,7 +34104,7 @@
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr"/>
-      <c r="C35" s="20" t="n">
+      <c r="C35" s="62" t="n">
         <v>46155</v>
       </c>
       <c r="D35" s="16" t="n">
@@ -32457,7 +34169,7 @@
           <t>GES-00007</t>
         </is>
       </c>
-      <c r="C36" s="20" t="n">
+      <c r="C36" s="62" t="n">
         <v>46152</v>
       </c>
       <c r="D36" s="16" t="n">
@@ -32522,7 +34234,7 @@
           <t>GES-00008</t>
         </is>
       </c>
-      <c r="C37" s="20" t="n">
+      <c r="C37" s="62" t="n">
         <v>46149</v>
       </c>
       <c r="D37" s="16" t="n">
@@ -32587,7 +34299,7 @@
           <t>GES-99999</t>
         </is>
       </c>
-      <c r="C38" s="20" t="n">
+      <c r="C38" s="62" t="n">
         <v>46146</v>
       </c>
       <c r="D38" s="16" t="n">
@@ -32652,7 +34364,7 @@
           <t>GES-00002</t>
         </is>
       </c>
-      <c r="C39" s="20" t="n">
+      <c r="C39" s="62" t="n">
         <v>46143</v>
       </c>
       <c r="D39" s="16" t="n">
@@ -32717,7 +34429,7 @@
           <t>GES-00003</t>
         </is>
       </c>
-      <c r="C40" s="20" t="n">
+      <c r="C40" s="62" t="n">
         <v>46140</v>
       </c>
       <c r="D40" s="16" t="n">
@@ -32782,7 +34494,7 @@
           <t>GES-00004</t>
         </is>
       </c>
-      <c r="C41" s="20" t="n">
+      <c r="C41" s="62" t="n">
         <v>46137</v>
       </c>
       <c r="D41" s="16" t="n">
@@ -32839,7 +34551,7 @@
     <row r="42">
       <c r="A42" s="15" t="n"/>
       <c r="B42" s="15" t="n"/>
-      <c r="C42" s="20" t="n"/>
+      <c r="C42" s="62" t="n"/>
       <c r="D42" s="16" t="n"/>
       <c r="E42" s="21" t="n"/>
       <c r="F42" s="16" t="n"/>
@@ -32884,7 +34596,7 @@
     <row r="43">
       <c r="A43" s="15" t="n"/>
       <c r="B43" s="15" t="n"/>
-      <c r="C43" s="20" t="n"/>
+      <c r="C43" s="62" t="n"/>
       <c r="D43" s="16" t="n"/>
       <c r="E43" s="21" t="n"/>
       <c r="F43" s="16" t="n"/>
@@ -32929,7 +34641,7 @@
     <row r="44">
       <c r="A44" s="15" t="n"/>
       <c r="B44" s="15" t="n"/>
-      <c r="C44" s="20" t="n"/>
+      <c r="C44" s="62" t="n"/>
       <c r="D44" s="16" t="n"/>
       <c r="E44" s="21" t="n"/>
       <c r="F44" s="16" t="n"/>
@@ -32974,7 +34686,7 @@
     <row r="45">
       <c r="A45" s="15" t="n"/>
       <c r="B45" s="15" t="n"/>
-      <c r="C45" s="20" t="n"/>
+      <c r="C45" s="62" t="n"/>
       <c r="D45" s="16" t="n"/>
       <c r="E45" s="21" t="n"/>
       <c r="F45" s="16" t="n"/>
@@ -33019,7 +34731,7 @@
     <row r="46">
       <c r="A46" s="15" t="n"/>
       <c r="B46" s="15" t="n"/>
-      <c r="C46" s="20" t="n"/>
+      <c r="C46" s="62" t="n"/>
       <c r="D46" s="16" t="n"/>
       <c r="E46" s="21" t="n"/>
       <c r="F46" s="16" t="n"/>
@@ -33064,7 +34776,7 @@
     <row r="47">
       <c r="A47" s="15" t="n"/>
       <c r="B47" s="15" t="n"/>
-      <c r="C47" s="20" t="n"/>
+      <c r="C47" s="62" t="n"/>
       <c r="D47" s="16" t="n"/>
       <c r="E47" s="21" t="n"/>
       <c r="F47" s="16" t="n"/>
@@ -33109,7 +34821,7 @@
     <row r="48">
       <c r="A48" s="15" t="n"/>
       <c r="B48" s="15" t="n"/>
-      <c r="C48" s="20" t="n"/>
+      <c r="C48" s="62" t="n"/>
       <c r="D48" s="16" t="n"/>
       <c r="E48" s="21" t="n"/>
       <c r="F48" s="16" t="n"/>
@@ -33154,7 +34866,7 @@
     <row r="49">
       <c r="A49" s="15" t="n"/>
       <c r="B49" s="15" t="n"/>
-      <c r="C49" s="20" t="n"/>
+      <c r="C49" s="62" t="n"/>
       <c r="D49" s="16" t="n"/>
       <c r="E49" s="21" t="n"/>
       <c r="F49" s="16" t="n"/>
@@ -33199,7 +34911,7 @@
     <row r="50">
       <c r="A50" s="15" t="n"/>
       <c r="B50" s="15" t="n"/>
-      <c r="C50" s="20" t="n"/>
+      <c r="C50" s="62" t="n"/>
       <c r="D50" s="16" t="n"/>
       <c r="E50" s="21" t="n"/>
       <c r="F50" s="16" t="n"/>
@@ -33244,7 +34956,7 @@
     <row r="51">
       <c r="A51" s="15" t="n"/>
       <c r="B51" s="15" t="n"/>
-      <c r="C51" s="20" t="n"/>
+      <c r="C51" s="62" t="n"/>
       <c r="D51" s="16" t="n"/>
       <c r="E51" s="21" t="n"/>
       <c r="F51" s="16" t="n"/>
@@ -33289,7 +35001,7 @@
     <row r="52">
       <c r="A52" s="15" t="n"/>
       <c r="B52" s="15" t="n"/>
-      <c r="C52" s="20" t="n"/>
+      <c r="C52" s="62" t="n"/>
       <c r="D52" s="16" t="n"/>
       <c r="E52" s="21" t="n"/>
       <c r="F52" s="16" t="n"/>
@@ -33334,7 +35046,7 @@
     <row r="53">
       <c r="A53" s="15" t="n"/>
       <c r="B53" s="15" t="n"/>
-      <c r="C53" s="20" t="n"/>
+      <c r="C53" s="62" t="n"/>
       <c r="D53" s="16" t="n"/>
       <c r="E53" s="21" t="n"/>
       <c r="F53" s="16" t="n"/>
@@ -33379,7 +35091,7 @@
     <row r="54">
       <c r="A54" s="15" t="n"/>
       <c r="B54" s="15" t="n"/>
-      <c r="C54" s="20" t="n"/>
+      <c r="C54" s="62" t="n"/>
       <c r="D54" s="16" t="n"/>
       <c r="E54" s="21" t="n"/>
       <c r="F54" s="16" t="n"/>
@@ -33424,7 +35136,7 @@
     <row r="55">
       <c r="A55" s="15" t="n"/>
       <c r="B55" s="15" t="n"/>
-      <c r="C55" s="20" t="n"/>
+      <c r="C55" s="62" t="n"/>
       <c r="D55" s="16" t="n"/>
       <c r="E55" s="21" t="n"/>
       <c r="F55" s="16" t="n"/>
@@ -33469,7 +35181,7 @@
     <row r="56">
       <c r="A56" s="15" t="n"/>
       <c r="B56" s="15" t="n"/>
-      <c r="C56" s="20" t="n"/>
+      <c r="C56" s="62" t="n"/>
       <c r="D56" s="16" t="n"/>
       <c r="E56" s="21" t="n"/>
       <c r="F56" s="16" t="n"/>
@@ -33514,7 +35226,7 @@
     <row r="57">
       <c r="A57" s="15" t="n"/>
       <c r="B57" s="15" t="n"/>
-      <c r="C57" s="20" t="n"/>
+      <c r="C57" s="62" t="n"/>
       <c r="D57" s="16" t="n"/>
       <c r="E57" s="21" t="n"/>
       <c r="F57" s="16" t="n"/>
@@ -33559,7 +35271,7 @@
     <row r="58">
       <c r="A58" s="15" t="n"/>
       <c r="B58" s="15" t="n"/>
-      <c r="C58" s="20" t="n"/>
+      <c r="C58" s="62" t="n"/>
       <c r="D58" s="16" t="n"/>
       <c r="E58" s="21" t="n"/>
       <c r="F58" s="16" t="n"/>
@@ -33604,7 +35316,7 @@
     <row r="59">
       <c r="A59" s="15" t="n"/>
       <c r="B59" s="15" t="n"/>
-      <c r="C59" s="20" t="n"/>
+      <c r="C59" s="62" t="n"/>
       <c r="D59" s="16" t="n"/>
       <c r="E59" s="21" t="n"/>
       <c r="F59" s="16" t="n"/>
@@ -33649,7 +35361,7 @@
     <row r="60">
       <c r="A60" s="15" t="n"/>
       <c r="B60" s="15" t="n"/>
-      <c r="C60" s="20" t="n"/>
+      <c r="C60" s="62" t="n"/>
       <c r="D60" s="16" t="n"/>
       <c r="E60" s="21" t="n"/>
       <c r="F60" s="16" t="n"/>
@@ -33694,7 +35406,7 @@
     <row r="61">
       <c r="A61" s="15" t="n"/>
       <c r="B61" s="15" t="n"/>
-      <c r="C61" s="20" t="n"/>
+      <c r="C61" s="62" t="n"/>
       <c r="D61" s="16" t="n"/>
       <c r="E61" s="21" t="n"/>
       <c r="F61" s="16" t="n"/>
@@ -33739,7 +35451,7 @@
     <row r="62">
       <c r="A62" s="15" t="n"/>
       <c r="B62" s="15" t="n"/>
-      <c r="C62" s="20" t="n"/>
+      <c r="C62" s="62" t="n"/>
       <c r="D62" s="16" t="n"/>
       <c r="E62" s="21" t="n"/>
       <c r="F62" s="16" t="n"/>
@@ -33784,7 +35496,7 @@
     <row r="63">
       <c r="A63" s="15" t="n"/>
       <c r="B63" s="15" t="n"/>
-      <c r="C63" s="20" t="n"/>
+      <c r="C63" s="62" t="n"/>
       <c r="D63" s="16" t="n"/>
       <c r="E63" s="21" t="n"/>
       <c r="F63" s="16" t="n"/>
@@ -33829,7 +35541,7 @@
     <row r="64">
       <c r="A64" s="15" t="n"/>
       <c r="B64" s="15" t="n"/>
-      <c r="C64" s="20" t="n"/>
+      <c r="C64" s="62" t="n"/>
       <c r="D64" s="16" t="n"/>
       <c r="E64" s="21" t="n"/>
       <c r="F64" s="16" t="n"/>
@@ -33874,7 +35586,7 @@
     <row r="65">
       <c r="A65" s="15" t="n"/>
       <c r="B65" s="15" t="n"/>
-      <c r="C65" s="20" t="n"/>
+      <c r="C65" s="62" t="n"/>
       <c r="D65" s="16" t="n"/>
       <c r="E65" s="21" t="n"/>
       <c r="F65" s="16" t="n"/>
@@ -33919,7 +35631,7 @@
     <row r="66">
       <c r="A66" s="15" t="n"/>
       <c r="B66" s="15" t="n"/>
-      <c r="C66" s="20" t="n"/>
+      <c r="C66" s="62" t="n"/>
       <c r="D66" s="16" t="n"/>
       <c r="E66" s="21" t="n"/>
       <c r="F66" s="16" t="n"/>
@@ -33964,7 +35676,7 @@
     <row r="67">
       <c r="A67" s="15" t="n"/>
       <c r="B67" s="15" t="n"/>
-      <c r="C67" s="20" t="n"/>
+      <c r="C67" s="62" t="n"/>
       <c r="D67" s="16" t="n"/>
       <c r="E67" s="21" t="n"/>
       <c r="F67" s="16" t="n"/>
@@ -34009,7 +35721,7 @@
     <row r="68">
       <c r="A68" s="15" t="n"/>
       <c r="B68" s="15" t="n"/>
-      <c r="C68" s="20" t="n"/>
+      <c r="C68" s="62" t="n"/>
       <c r="D68" s="16" t="n"/>
       <c r="E68" s="21" t="n"/>
       <c r="F68" s="16" t="n"/>
@@ -34054,7 +35766,7 @@
     <row r="69">
       <c r="A69" s="15" t="n"/>
       <c r="B69" s="15" t="n"/>
-      <c r="C69" s="20" t="n"/>
+      <c r="C69" s="62" t="n"/>
       <c r="D69" s="16" t="n"/>
       <c r="E69" s="21" t="n"/>
       <c r="F69" s="16" t="n"/>
@@ -34099,7 +35811,7 @@
     <row r="70">
       <c r="A70" s="15" t="n"/>
       <c r="B70" s="15" t="n"/>
-      <c r="C70" s="20" t="n"/>
+      <c r="C70" s="62" t="n"/>
       <c r="D70" s="16" t="n"/>
       <c r="E70" s="21" t="n"/>
       <c r="F70" s="16" t="n"/>
@@ -34144,7 +35856,7 @@
     <row r="71">
       <c r="A71" s="15" t="n"/>
       <c r="B71" s="15" t="n"/>
-      <c r="C71" s="20" t="n"/>
+      <c r="C71" s="62" t="n"/>
       <c r="D71" s="16" t="n"/>
       <c r="E71" s="21" t="n"/>
       <c r="F71" s="16" t="n"/>
@@ -34189,7 +35901,7 @@
     <row r="72">
       <c r="A72" s="15" t="n"/>
       <c r="B72" s="15" t="n"/>
-      <c r="C72" s="20" t="n"/>
+      <c r="C72" s="62" t="n"/>
       <c r="D72" s="16" t="n"/>
       <c r="E72" s="21" t="n"/>
       <c r="F72" s="16" t="n"/>
@@ -34234,7 +35946,7 @@
     <row r="73">
       <c r="A73" s="15" t="n"/>
       <c r="B73" s="15" t="n"/>
-      <c r="C73" s="20" t="n"/>
+      <c r="C73" s="62" t="n"/>
       <c r="D73" s="16" t="n"/>
       <c r="E73" s="21" t="n"/>
       <c r="F73" s="16" t="n"/>
@@ -34279,7 +35991,7 @@
     <row r="74">
       <c r="A74" s="15" t="n"/>
       <c r="B74" s="15" t="n"/>
-      <c r="C74" s="20" t="n"/>
+      <c r="C74" s="62" t="n"/>
       <c r="D74" s="16" t="n"/>
       <c r="E74" s="21" t="n"/>
       <c r="F74" s="16" t="n"/>
@@ -34324,7 +36036,7 @@
     <row r="75">
       <c r="A75" s="15" t="n"/>
       <c r="B75" s="15" t="n"/>
-      <c r="C75" s="20" t="n"/>
+      <c r="C75" s="62" t="n"/>
       <c r="D75" s="16" t="n"/>
       <c r="E75" s="21" t="n"/>
       <c r="F75" s="16" t="n"/>
@@ -34369,7 +36081,7 @@
     <row r="76">
       <c r="A76" s="15" t="n"/>
       <c r="B76" s="15" t="n"/>
-      <c r="C76" s="20" t="n"/>
+      <c r="C76" s="62" t="n"/>
       <c r="D76" s="16" t="n"/>
       <c r="E76" s="21" t="n"/>
       <c r="F76" s="16" t="n"/>
@@ -34414,7 +36126,7 @@
     <row r="77">
       <c r="A77" s="15" t="n"/>
       <c r="B77" s="15" t="n"/>
-      <c r="C77" s="20" t="n"/>
+      <c r="C77" s="62" t="n"/>
       <c r="D77" s="16" t="n"/>
       <c r="E77" s="21" t="n"/>
       <c r="F77" s="16" t="n"/>
@@ -34459,7 +36171,7 @@
     <row r="78">
       <c r="A78" s="15" t="n"/>
       <c r="B78" s="15" t="n"/>
-      <c r="C78" s="20" t="n"/>
+      <c r="C78" s="62" t="n"/>
       <c r="D78" s="16" t="n"/>
       <c r="E78" s="21" t="n"/>
       <c r="F78" s="16" t="n"/>
@@ -34504,7 +36216,7 @@
     <row r="79">
       <c r="A79" s="15" t="n"/>
       <c r="B79" s="15" t="n"/>
-      <c r="C79" s="20" t="n"/>
+      <c r="C79" s="62" t="n"/>
       <c r="D79" s="16" t="n"/>
       <c r="E79" s="21" t="n"/>
       <c r="F79" s="16" t="n"/>
@@ -34549,7 +36261,7 @@
     <row r="80">
       <c r="A80" s="15" t="n"/>
       <c r="B80" s="15" t="n"/>
-      <c r="C80" s="20" t="n"/>
+      <c r="C80" s="62" t="n"/>
       <c r="D80" s="16" t="n"/>
       <c r="E80" s="21" t="n"/>
       <c r="F80" s="16" t="n"/>
@@ -34594,7 +36306,7 @@
     <row r="81">
       <c r="A81" s="15" t="n"/>
       <c r="B81" s="15" t="n"/>
-      <c r="C81" s="20" t="n"/>
+      <c r="C81" s="62" t="n"/>
       <c r="D81" s="16" t="n"/>
       <c r="E81" s="21" t="n"/>
       <c r="F81" s="16" t="n"/>
@@ -34639,7 +36351,7 @@
     <row r="82">
       <c r="A82" s="15" t="n"/>
       <c r="B82" s="15" t="n"/>
-      <c r="C82" s="20" t="n"/>
+      <c r="C82" s="62" t="n"/>
       <c r="D82" s="16" t="n"/>
       <c r="E82" s="21" t="n"/>
       <c r="F82" s="16" t="n"/>
@@ -34684,7 +36396,7 @@
     <row r="83">
       <c r="A83" s="15" t="n"/>
       <c r="B83" s="15" t="n"/>
-      <c r="C83" s="20" t="n"/>
+      <c r="C83" s="62" t="n"/>
       <c r="D83" s="16" t="n"/>
       <c r="E83" s="21" t="n"/>
       <c r="F83" s="16" t="n"/>
@@ -34729,7 +36441,7 @@
     <row r="84">
       <c r="A84" s="15" t="n"/>
       <c r="B84" s="15" t="n"/>
-      <c r="C84" s="20" t="n"/>
+      <c r="C84" s="62" t="n"/>
       <c r="D84" s="16" t="n"/>
       <c r="E84" s="21" t="n"/>
       <c r="F84" s="16" t="n"/>
@@ -34774,7 +36486,7 @@
     <row r="85">
       <c r="A85" s="15" t="n"/>
       <c r="B85" s="15" t="n"/>
-      <c r="C85" s="20" t="n"/>
+      <c r="C85" s="62" t="n"/>
       <c r="D85" s="16" t="n"/>
       <c r="E85" s="21" t="n"/>
       <c r="F85" s="16" t="n"/>
@@ -34819,7 +36531,7 @@
     <row r="86">
       <c r="A86" s="15" t="n"/>
       <c r="B86" s="15" t="n"/>
-      <c r="C86" s="20" t="n"/>
+      <c r="C86" s="62" t="n"/>
       <c r="D86" s="16" t="n"/>
       <c r="E86" s="21" t="n"/>
       <c r="F86" s="16" t="n"/>
@@ -34864,7 +36576,7 @@
     <row r="87">
       <c r="A87" s="15" t="n"/>
       <c r="B87" s="15" t="n"/>
-      <c r="C87" s="20" t="n"/>
+      <c r="C87" s="62" t="n"/>
       <c r="D87" s="16" t="n"/>
       <c r="E87" s="21" t="n"/>
       <c r="F87" s="16" t="n"/>
@@ -34909,7 +36621,7 @@
     <row r="88">
       <c r="A88" s="15" t="n"/>
       <c r="B88" s="15" t="n"/>
-      <c r="C88" s="20" t="n"/>
+      <c r="C88" s="62" t="n"/>
       <c r="D88" s="16" t="n"/>
       <c r="E88" s="21" t="n"/>
       <c r="F88" s="16" t="n"/>
@@ -34954,7 +36666,7 @@
     <row r="89">
       <c r="A89" s="15" t="n"/>
       <c r="B89" s="15" t="n"/>
-      <c r="C89" s="20" t="n"/>
+      <c r="C89" s="62" t="n"/>
       <c r="D89" s="16" t="n"/>
       <c r="E89" s="21" t="n"/>
       <c r="F89" s="16" t="n"/>
@@ -34999,7 +36711,7 @@
     <row r="90">
       <c r="A90" s="15" t="n"/>
       <c r="B90" s="15" t="n"/>
-      <c r="C90" s="20" t="n"/>
+      <c r="C90" s="62" t="n"/>
       <c r="D90" s="16" t="n"/>
       <c r="E90" s="21" t="n"/>
       <c r="F90" s="16" t="n"/>
@@ -35044,7 +36756,7 @@
     <row r="91">
       <c r="A91" s="15" t="n"/>
       <c r="B91" s="15" t="n"/>
-      <c r="C91" s="20" t="n"/>
+      <c r="C91" s="62" t="n"/>
       <c r="D91" s="16" t="n"/>
       <c r="E91" s="21" t="n"/>
       <c r="F91" s="16" t="n"/>
@@ -35089,7 +36801,7 @@
     <row r="92">
       <c r="A92" s="15" t="n"/>
       <c r="B92" s="15" t="n"/>
-      <c r="C92" s="20" t="n"/>
+      <c r="C92" s="62" t="n"/>
       <c r="D92" s="16" t="n"/>
       <c r="E92" s="21" t="n"/>
       <c r="F92" s="16" t="n"/>
@@ -35134,7 +36846,7 @@
     <row r="93">
       <c r="A93" s="15" t="n"/>
       <c r="B93" s="15" t="n"/>
-      <c r="C93" s="20" t="n"/>
+      <c r="C93" s="62" t="n"/>
       <c r="D93" s="16" t="n"/>
       <c r="E93" s="21" t="n"/>
       <c r="F93" s="16" t="n"/>
@@ -35179,7 +36891,7 @@
     <row r="94">
       <c r="A94" s="15" t="n"/>
       <c r="B94" s="15" t="n"/>
-      <c r="C94" s="20" t="n"/>
+      <c r="C94" s="62" t="n"/>
       <c r="D94" s="16" t="n"/>
       <c r="E94" s="21" t="n"/>
       <c r="F94" s="16" t="n"/>
@@ -35224,7 +36936,7 @@
     <row r="95">
       <c r="A95" s="15" t="n"/>
       <c r="B95" s="15" t="n"/>
-      <c r="C95" s="20" t="n"/>
+      <c r="C95" s="62" t="n"/>
       <c r="D95" s="16" t="n"/>
       <c r="E95" s="21" t="n"/>
       <c r="F95" s="16" t="n"/>
@@ -35269,7 +36981,7 @@
     <row r="96">
       <c r="A96" s="15" t="n"/>
       <c r="B96" s="15" t="n"/>
-      <c r="C96" s="20" t="n"/>
+      <c r="C96" s="62" t="n"/>
       <c r="D96" s="16" t="n"/>
       <c r="E96" s="21" t="n"/>
       <c r="F96" s="16" t="n"/>
@@ -35314,7 +37026,7 @@
     <row r="97">
       <c r="A97" s="15" t="n"/>
       <c r="B97" s="15" t="n"/>
-      <c r="C97" s="20" t="n"/>
+      <c r="C97" s="62" t="n"/>
       <c r="D97" s="16" t="n"/>
       <c r="E97" s="21" t="n"/>
       <c r="F97" s="16" t="n"/>
@@ -35359,7 +37071,7 @@
     <row r="98">
       <c r="A98" s="15" t="n"/>
       <c r="B98" s="15" t="n"/>
-      <c r="C98" s="20" t="n"/>
+      <c r="C98" s="62" t="n"/>
       <c r="D98" s="16" t="n"/>
       <c r="E98" s="21" t="n"/>
       <c r="F98" s="16" t="n"/>
@@ -35404,7 +37116,7 @@
     <row r="99">
       <c r="A99" s="15" t="n"/>
       <c r="B99" s="15" t="n"/>
-      <c r="C99" s="20" t="n"/>
+      <c r="C99" s="62" t="n"/>
       <c r="D99" s="16" t="n"/>
       <c r="E99" s="21" t="n"/>
       <c r="F99" s="16" t="n"/>
@@ -35449,7 +37161,7 @@
     <row r="100">
       <c r="A100" s="15" t="n"/>
       <c r="B100" s="15" t="n"/>
-      <c r="C100" s="20" t="n"/>
+      <c r="C100" s="62" t="n"/>
       <c r="D100" s="16" t="n"/>
       <c r="E100" s="21" t="n"/>
       <c r="F100" s="16" t="n"/>
@@ -35494,7 +37206,7 @@
     <row r="101">
       <c r="A101" s="15" t="n"/>
       <c r="B101" s="15" t="n"/>
-      <c r="C101" s="20" t="n"/>
+      <c r="C101" s="62" t="n"/>
       <c r="D101" s="16" t="n"/>
       <c r="E101" s="21" t="n"/>
       <c r="F101" s="16" t="n"/>
@@ -35539,7 +37251,7 @@
     <row r="102">
       <c r="A102" s="15" t="n"/>
       <c r="B102" s="15" t="n"/>
-      <c r="C102" s="20" t="n"/>
+      <c r="C102" s="62" t="n"/>
       <c r="D102" s="16" t="n"/>
       <c r="E102" s="21" t="n"/>
       <c r="F102" s="16" t="n"/>
@@ -35584,7 +37296,7 @@
     <row r="103">
       <c r="A103" s="15" t="n"/>
       <c r="B103" s="15" t="n"/>
-      <c r="C103" s="20" t="n"/>
+      <c r="C103" s="62" t="n"/>
       <c r="D103" s="16" t="n"/>
       <c r="E103" s="21" t="n"/>
       <c r="F103" s="16" t="n"/>
@@ -35629,7 +37341,7 @@
     <row r="104">
       <c r="A104" s="15" t="n"/>
       <c r="B104" s="15" t="n"/>
-      <c r="C104" s="20" t="n"/>
+      <c r="C104" s="62" t="n"/>
       <c r="D104" s="16" t="n"/>
       <c r="E104" s="21" t="n"/>
       <c r="F104" s="16" t="n"/>
@@ -35674,7 +37386,7 @@
     <row r="105">
       <c r="A105" s="15" t="n"/>
       <c r="B105" s="15" t="n"/>
-      <c r="C105" s="20" t="n"/>
+      <c r="C105" s="62" t="n"/>
       <c r="D105" s="16" t="n"/>
       <c r="E105" s="21" t="n"/>
       <c r="F105" s="16" t="n"/>
@@ -35719,7 +37431,7 @@
     <row r="106">
       <c r="A106" s="15" t="n"/>
       <c r="B106" s="15" t="n"/>
-      <c r="C106" s="20" t="n"/>
+      <c r="C106" s="62" t="n"/>
       <c r="D106" s="16" t="n"/>
       <c r="E106" s="21" t="n"/>
       <c r="F106" s="16" t="n"/>
@@ -35764,7 +37476,7 @@
     <row r="107">
       <c r="A107" s="15" t="n"/>
       <c r="B107" s="15" t="n"/>
-      <c r="C107" s="20" t="n"/>
+      <c r="C107" s="62" t="n"/>
       <c r="D107" s="16" t="n"/>
       <c r="E107" s="21" t="n"/>
       <c r="F107" s="16" t="n"/>
@@ -35809,7 +37521,7 @@
     <row r="108">
       <c r="A108" s="15" t="n"/>
       <c r="B108" s="15" t="n"/>
-      <c r="C108" s="20" t="n"/>
+      <c r="C108" s="62" t="n"/>
       <c r="D108" s="16" t="n"/>
       <c r="E108" s="21" t="n"/>
       <c r="F108" s="16" t="n"/>
@@ -35854,7 +37566,7 @@
     <row r="109">
       <c r="A109" s="15" t="n"/>
       <c r="B109" s="15" t="n"/>
-      <c r="C109" s="20" t="n"/>
+      <c r="C109" s="62" t="n"/>
       <c r="D109" s="16" t="n"/>
       <c r="E109" s="21" t="n"/>
       <c r="F109" s="16" t="n"/>
@@ -35899,7 +37611,7 @@
     <row r="110">
       <c r="A110" s="15" t="n"/>
       <c r="B110" s="15" t="n"/>
-      <c r="C110" s="20" t="n"/>
+      <c r="C110" s="62" t="n"/>
       <c r="D110" s="16" t="n"/>
       <c r="E110" s="21" t="n"/>
       <c r="F110" s="16" t="n"/>
@@ -35944,7 +37656,7 @@
     <row r="111">
       <c r="A111" s="15" t="n"/>
       <c r="B111" s="15" t="n"/>
-      <c r="C111" s="20" t="n"/>
+      <c r="C111" s="62" t="n"/>
       <c r="D111" s="16" t="n"/>
       <c r="E111" s="21" t="n"/>
       <c r="F111" s="16" t="n"/>
@@ -35989,7 +37701,7 @@
     <row r="112">
       <c r="A112" s="15" t="n"/>
       <c r="B112" s="15" t="n"/>
-      <c r="C112" s="20" t="n"/>
+      <c r="C112" s="62" t="n"/>
       <c r="D112" s="16" t="n"/>
       <c r="E112" s="21" t="n"/>
       <c r="F112" s="16" t="n"/>
@@ -36034,7 +37746,7 @@
     <row r="113">
       <c r="A113" s="15" t="n"/>
       <c r="B113" s="15" t="n"/>
-      <c r="C113" s="20" t="n"/>
+      <c r="C113" s="62" t="n"/>
       <c r="D113" s="16" t="n"/>
       <c r="E113" s="21" t="n"/>
       <c r="F113" s="16" t="n"/>
@@ -36079,7 +37791,7 @@
     <row r="114">
       <c r="A114" s="15" t="n"/>
       <c r="B114" s="15" t="n"/>
-      <c r="C114" s="20" t="n"/>
+      <c r="C114" s="62" t="n"/>
       <c r="D114" s="16" t="n"/>
       <c r="E114" s="21" t="n"/>
       <c r="F114" s="16" t="n"/>
@@ -36124,7 +37836,7 @@
     <row r="115">
       <c r="A115" s="15" t="n"/>
       <c r="B115" s="15" t="n"/>
-      <c r="C115" s="20" t="n"/>
+      <c r="C115" s="62" t="n"/>
       <c r="D115" s="16" t="n"/>
       <c r="E115" s="21" t="n"/>
       <c r="F115" s="16" t="n"/>
@@ -36169,7 +37881,7 @@
     <row r="116">
       <c r="A116" s="15" t="n"/>
       <c r="B116" s="15" t="n"/>
-      <c r="C116" s="20" t="n"/>
+      <c r="C116" s="62" t="n"/>
       <c r="D116" s="16" t="n"/>
       <c r="E116" s="21" t="n"/>
       <c r="F116" s="16" t="n"/>
@@ -36214,7 +37926,7 @@
     <row r="117">
       <c r="A117" s="15" t="n"/>
       <c r="B117" s="15" t="n"/>
-      <c r="C117" s="20" t="n"/>
+      <c r="C117" s="62" t="n"/>
       <c r="D117" s="16" t="n"/>
       <c r="E117" s="21" t="n"/>
       <c r="F117" s="16" t="n"/>
@@ -36259,7 +37971,7 @@
     <row r="118">
       <c r="A118" s="15" t="n"/>
       <c r="B118" s="15" t="n"/>
-      <c r="C118" s="20" t="n"/>
+      <c r="C118" s="62" t="n"/>
       <c r="D118" s="16" t="n"/>
       <c r="E118" s="21" t="n"/>
       <c r="F118" s="16" t="n"/>
@@ -36304,7 +38016,7 @@
     <row r="119">
       <c r="A119" s="15" t="n"/>
       <c r="B119" s="15" t="n"/>
-      <c r="C119" s="20" t="n"/>
+      <c r="C119" s="62" t="n"/>
       <c r="D119" s="16" t="n"/>
       <c r="E119" s="21" t="n"/>
       <c r="F119" s="16" t="n"/>
@@ -36349,7 +38061,7 @@
     <row r="120">
       <c r="A120" s="15" t="n"/>
       <c r="B120" s="15" t="n"/>
-      <c r="C120" s="20" t="n"/>
+      <c r="C120" s="62" t="n"/>
       <c r="D120" s="16" t="n"/>
       <c r="E120" s="21" t="n"/>
       <c r="F120" s="16" t="n"/>
@@ -36394,7 +38106,7 @@
     <row r="121">
       <c r="A121" s="15" t="n"/>
       <c r="B121" s="15" t="n"/>
-      <c r="C121" s="20" t="n"/>
+      <c r="C121" s="62" t="n"/>
       <c r="D121" s="16" t="n"/>
       <c r="E121" s="21" t="n"/>
       <c r="F121" s="16" t="n"/>
@@ -36439,7 +38151,7 @@
     <row r="122">
       <c r="A122" s="15" t="n"/>
       <c r="B122" s="15" t="n"/>
-      <c r="C122" s="20" t="n"/>
+      <c r="C122" s="62" t="n"/>
       <c r="D122" s="16" t="n"/>
       <c r="E122" s="21" t="n"/>
       <c r="F122" s="16" t="n"/>
@@ -36484,7 +38196,7 @@
     <row r="123">
       <c r="A123" s="15" t="n"/>
       <c r="B123" s="15" t="n"/>
-      <c r="C123" s="20" t="n"/>
+      <c r="C123" s="62" t="n"/>
       <c r="D123" s="16" t="n"/>
       <c r="E123" s="21" t="n"/>
       <c r="F123" s="16" t="n"/>
@@ -36529,7 +38241,7 @@
     <row r="124">
       <c r="A124" s="15" t="n"/>
       <c r="B124" s="15" t="n"/>
-      <c r="C124" s="20" t="n"/>
+      <c r="C124" s="62" t="n"/>
       <c r="D124" s="16" t="n"/>
       <c r="E124" s="21" t="n"/>
       <c r="F124" s="16" t="n"/>
@@ -36574,7 +38286,7 @@
     <row r="125">
       <c r="A125" s="15" t="n"/>
       <c r="B125" s="15" t="n"/>
-      <c r="C125" s="20" t="n"/>
+      <c r="C125" s="62" t="n"/>
       <c r="D125" s="16" t="n"/>
       <c r="E125" s="21" t="n"/>
       <c r="F125" s="16" t="n"/>
@@ -36619,7 +38331,7 @@
     <row r="126">
       <c r="A126" s="15" t="n"/>
       <c r="B126" s="15" t="n"/>
-      <c r="C126" s="20" t="n"/>
+      <c r="C126" s="62" t="n"/>
       <c r="D126" s="16" t="n"/>
       <c r="E126" s="21" t="n"/>
       <c r="F126" s="16" t="n"/>
@@ -36664,7 +38376,7 @@
     <row r="127">
       <c r="A127" s="15" t="n"/>
       <c r="B127" s="15" t="n"/>
-      <c r="C127" s="20" t="n"/>
+      <c r="C127" s="62" t="n"/>
       <c r="D127" s="16" t="n"/>
       <c r="E127" s="21" t="n"/>
       <c r="F127" s="16" t="n"/>
@@ -36709,7 +38421,7 @@
     <row r="128">
       <c r="A128" s="15" t="n"/>
       <c r="B128" s="15" t="n"/>
-      <c r="C128" s="20" t="n"/>
+      <c r="C128" s="62" t="n"/>
       <c r="D128" s="16" t="n"/>
       <c r="E128" s="21" t="n"/>
       <c r="F128" s="16" t="n"/>
@@ -36754,7 +38466,7 @@
     <row r="129">
       <c r="A129" s="15" t="n"/>
       <c r="B129" s="15" t="n"/>
-      <c r="C129" s="20" t="n"/>
+      <c r="C129" s="62" t="n"/>
       <c r="D129" s="16" t="n"/>
       <c r="E129" s="21" t="n"/>
       <c r="F129" s="16" t="n"/>
@@ -36799,7 +38511,7 @@
     <row r="130">
       <c r="A130" s="15" t="n"/>
       <c r="B130" s="15" t="n"/>
-      <c r="C130" s="20" t="n"/>
+      <c r="C130" s="62" t="n"/>
       <c r="D130" s="16" t="n"/>
       <c r="E130" s="21" t="n"/>
       <c r="F130" s="16" t="n"/>
@@ -36844,7 +38556,7 @@
     <row r="131">
       <c r="A131" s="15" t="n"/>
       <c r="B131" s="15" t="n"/>
-      <c r="C131" s="20" t="n"/>
+      <c r="C131" s="62" t="n"/>
       <c r="D131" s="16" t="n"/>
       <c r="E131" s="21" t="n"/>
       <c r="F131" s="16" t="n"/>
@@ -36889,7 +38601,7 @@
     <row r="132">
       <c r="A132" s="15" t="n"/>
       <c r="B132" s="15" t="n"/>
-      <c r="C132" s="20" t="n"/>
+      <c r="C132" s="62" t="n"/>
       <c r="D132" s="16" t="n"/>
       <c r="E132" s="21" t="n"/>
       <c r="F132" s="16" t="n"/>
@@ -36934,7 +38646,7 @@
     <row r="133">
       <c r="A133" s="15" t="n"/>
       <c r="B133" s="15" t="n"/>
-      <c r="C133" s="20" t="n"/>
+      <c r="C133" s="62" t="n"/>
       <c r="D133" s="16" t="n"/>
       <c r="E133" s="21" t="n"/>
       <c r="F133" s="16" t="n"/>
@@ -36979,7 +38691,7 @@
     <row r="134">
       <c r="A134" s="15" t="n"/>
       <c r="B134" s="15" t="n"/>
-      <c r="C134" s="20" t="n"/>
+      <c r="C134" s="62" t="n"/>
       <c r="D134" s="16" t="n"/>
       <c r="E134" s="21" t="n"/>
       <c r="F134" s="16" t="n"/>
@@ -37024,7 +38736,7 @@
     <row r="135">
       <c r="A135" s="15" t="n"/>
       <c r="B135" s="15" t="n"/>
-      <c r="C135" s="20" t="n"/>
+      <c r="C135" s="62" t="n"/>
       <c r="D135" s="16" t="n"/>
       <c r="E135" s="21" t="n"/>
       <c r="F135" s="16" t="n"/>
@@ -37069,7 +38781,7 @@
     <row r="136">
       <c r="A136" s="15" t="n"/>
       <c r="B136" s="15" t="n"/>
-      <c r="C136" s="20" t="n"/>
+      <c r="C136" s="62" t="n"/>
       <c r="D136" s="16" t="n"/>
       <c r="E136" s="21" t="n"/>
       <c r="F136" s="16" t="n"/>
@@ -37114,7 +38826,7 @@
     <row r="137">
       <c r="A137" s="15" t="n"/>
       <c r="B137" s="15" t="n"/>
-      <c r="C137" s="20" t="n"/>
+      <c r="C137" s="62" t="n"/>
       <c r="D137" s="16" t="n"/>
       <c r="E137" s="21" t="n"/>
       <c r="F137" s="16" t="n"/>
@@ -37159,7 +38871,7 @@
     <row r="138">
       <c r="A138" s="15" t="n"/>
       <c r="B138" s="15" t="n"/>
-      <c r="C138" s="20" t="n"/>
+      <c r="C138" s="62" t="n"/>
       <c r="D138" s="16" t="n"/>
       <c r="E138" s="21" t="n"/>
       <c r="F138" s="16" t="n"/>
@@ -37204,7 +38916,7 @@
     <row r="139">
       <c r="A139" s="15" t="n"/>
       <c r="B139" s="15" t="n"/>
-      <c r="C139" s="20" t="n"/>
+      <c r="C139" s="62" t="n"/>
       <c r="D139" s="16" t="n"/>
       <c r="E139" s="21" t="n"/>
       <c r="F139" s="16" t="n"/>
@@ -37249,7 +38961,7 @@
     <row r="140">
       <c r="A140" s="15" t="n"/>
       <c r="B140" s="15" t="n"/>
-      <c r="C140" s="20" t="n"/>
+      <c r="C140" s="62" t="n"/>
       <c r="D140" s="16" t="n"/>
       <c r="E140" s="21" t="n"/>
       <c r="F140" s="16" t="n"/>
@@ -37294,7 +39006,7 @@
     <row r="141">
       <c r="A141" s="15" t="n"/>
       <c r="B141" s="15" t="n"/>
-      <c r="C141" s="20" t="n"/>
+      <c r="C141" s="62" t="n"/>
       <c r="D141" s="16" t="n"/>
       <c r="E141" s="21" t="n"/>
       <c r="F141" s="16" t="n"/>
@@ -37339,7 +39051,7 @@
     <row r="142">
       <c r="A142" s="15" t="n"/>
       <c r="B142" s="15" t="n"/>
-      <c r="C142" s="20" t="n"/>
+      <c r="C142" s="62" t="n"/>
       <c r="D142" s="16" t="n"/>
       <c r="E142" s="21" t="n"/>
       <c r="F142" s="16" t="n"/>
@@ -37384,7 +39096,7 @@
     <row r="143">
       <c r="A143" s="15" t="n"/>
       <c r="B143" s="15" t="n"/>
-      <c r="C143" s="20" t="n"/>
+      <c r="C143" s="62" t="n"/>
       <c r="D143" s="16" t="n"/>
       <c r="E143" s="21" t="n"/>
       <c r="F143" s="16" t="n"/>
@@ -37429,7 +39141,7 @@
     <row r="144">
       <c r="A144" s="15" t="n"/>
       <c r="B144" s="15" t="n"/>
-      <c r="C144" s="20" t="n"/>
+      <c r="C144" s="62" t="n"/>
       <c r="D144" s="16" t="n"/>
       <c r="E144" s="21" t="n"/>
       <c r="F144" s="16" t="n"/>
@@ -37474,7 +39186,7 @@
     <row r="145">
       <c r="A145" s="15" t="n"/>
       <c r="B145" s="15" t="n"/>
-      <c r="C145" s="20" t="n"/>
+      <c r="C145" s="62" t="n"/>
       <c r="D145" s="16" t="n"/>
       <c r="E145" s="21" t="n"/>
       <c r="F145" s="16" t="n"/>
@@ -37519,7 +39231,7 @@
     <row r="146">
       <c r="A146" s="15" t="n"/>
       <c r="B146" s="15" t="n"/>
-      <c r="C146" s="20" t="n"/>
+      <c r="C146" s="62" t="n"/>
       <c r="D146" s="16" t="n"/>
       <c r="E146" s="21" t="n"/>
       <c r="F146" s="16" t="n"/>
@@ -37564,7 +39276,7 @@
     <row r="147">
       <c r="A147" s="15" t="n"/>
       <c r="B147" s="15" t="n"/>
-      <c r="C147" s="20" t="n"/>
+      <c r="C147" s="62" t="n"/>
       <c r="D147" s="16" t="n"/>
       <c r="E147" s="21" t="n"/>
       <c r="F147" s="16" t="n"/>
@@ -37609,7 +39321,7 @@
     <row r="148">
       <c r="A148" s="15" t="n"/>
       <c r="B148" s="15" t="n"/>
-      <c r="C148" s="20" t="n"/>
+      <c r="C148" s="62" t="n"/>
       <c r="D148" s="16" t="n"/>
       <c r="E148" s="21" t="n"/>
       <c r="F148" s="16" t="n"/>
@@ -37654,7 +39366,7 @@
     <row r="149">
       <c r="A149" s="15" t="n"/>
       <c r="B149" s="15" t="n"/>
-      <c r="C149" s="20" t="n"/>
+      <c r="C149" s="62" t="n"/>
       <c r="D149" s="16" t="n"/>
       <c r="E149" s="21" t="n"/>
       <c r="F149" s="16" t="n"/>
@@ -37699,7 +39411,7 @@
     <row r="150">
       <c r="A150" s="15" t="n"/>
       <c r="B150" s="15" t="n"/>
-      <c r="C150" s="20" t="n"/>
+      <c r="C150" s="62" t="n"/>
       <c r="D150" s="16" t="n"/>
       <c r="E150" s="21" t="n"/>
       <c r="F150" s="16" t="n"/>
@@ -37744,7 +39456,7 @@
     <row r="151">
       <c r="A151" s="15" t="n"/>
       <c r="B151" s="15" t="n"/>
-      <c r="C151" s="20" t="n"/>
+      <c r="C151" s="62" t="n"/>
       <c r="D151" s="16" t="n"/>
       <c r="E151" s="21" t="n"/>
       <c r="F151" s="16" t="n"/>
@@ -37789,7 +39501,7 @@
     <row r="152">
       <c r="A152" s="15" t="n"/>
       <c r="B152" s="15" t="n"/>
-      <c r="C152" s="20" t="n"/>
+      <c r="C152" s="62" t="n"/>
       <c r="D152" s="16" t="n"/>
       <c r="E152" s="21" t="n"/>
       <c r="F152" s="16" t="n"/>
@@ -37834,7 +39546,7 @@
     <row r="153">
       <c r="A153" s="15" t="n"/>
       <c r="B153" s="15" t="n"/>
-      <c r="C153" s="20" t="n"/>
+      <c r="C153" s="62" t="n"/>
       <c r="D153" s="16" t="n"/>
       <c r="E153" s="21" t="n"/>
       <c r="F153" s="16" t="n"/>
@@ -37879,7 +39591,7 @@
     <row r="154">
       <c r="A154" s="15" t="n"/>
       <c r="B154" s="15" t="n"/>
-      <c r="C154" s="20" t="n"/>
+      <c r="C154" s="62" t="n"/>
       <c r="D154" s="16" t="n"/>
       <c r="E154" s="21" t="n"/>
       <c r="F154" s="16" t="n"/>
@@ -37924,7 +39636,7 @@
     <row r="155">
       <c r="A155" s="15" t="n"/>
       <c r="B155" s="15" t="n"/>
-      <c r="C155" s="20" t="n"/>
+      <c r="C155" s="62" t="n"/>
       <c r="D155" s="16" t="n"/>
       <c r="E155" s="21" t="n"/>
       <c r="F155" s="16" t="n"/>
@@ -37969,7 +39681,7 @@
     <row r="156">
       <c r="A156" s="15" t="n"/>
       <c r="B156" s="15" t="n"/>
-      <c r="C156" s="20" t="n"/>
+      <c r="C156" s="62" t="n"/>
       <c r="D156" s="16" t="n"/>
       <c r="E156" s="21" t="n"/>
       <c r="F156" s="16" t="n"/>
@@ -38014,7 +39726,7 @@
     <row r="157">
       <c r="A157" s="15" t="n"/>
       <c r="B157" s="15" t="n"/>
-      <c r="C157" s="20" t="n"/>
+      <c r="C157" s="62" t="n"/>
       <c r="D157" s="16" t="n"/>
       <c r="E157" s="21" t="n"/>
       <c r="F157" s="16" t="n"/>
@@ -38059,7 +39771,7 @@
     <row r="158">
       <c r="A158" s="15" t="n"/>
       <c r="B158" s="15" t="n"/>
-      <c r="C158" s="20" t="n"/>
+      <c r="C158" s="62" t="n"/>
       <c r="D158" s="16" t="n"/>
       <c r="E158" s="21" t="n"/>
       <c r="F158" s="16" t="n"/>
@@ -38104,7 +39816,7 @@
     <row r="159">
       <c r="A159" s="15" t="n"/>
       <c r="B159" s="15" t="n"/>
-      <c r="C159" s="20" t="n"/>
+      <c r="C159" s="62" t="n"/>
       <c r="D159" s="16" t="n"/>
       <c r="E159" s="21" t="n"/>
       <c r="F159" s="16" t="n"/>
@@ -38149,7 +39861,7 @@
     <row r="160">
       <c r="A160" s="15" t="n"/>
       <c r="B160" s="15" t="n"/>
-      <c r="C160" s="20" t="n"/>
+      <c r="C160" s="62" t="n"/>
       <c r="D160" s="16" t="n"/>
       <c r="E160" s="21" t="n"/>
       <c r="F160" s="16" t="n"/>
@@ -38194,7 +39906,7 @@
     <row r="161">
       <c r="A161" s="15" t="n"/>
       <c r="B161" s="15" t="n"/>
-      <c r="C161" s="20" t="n"/>
+      <c r="C161" s="62" t="n"/>
       <c r="D161" s="16" t="n"/>
       <c r="E161" s="21" t="n"/>
       <c r="F161" s="16" t="n"/>
@@ -38239,7 +39951,7 @@
     <row r="162">
       <c r="A162" s="15" t="n"/>
       <c r="B162" s="15" t="n"/>
-      <c r="C162" s="20" t="n"/>
+      <c r="C162" s="62" t="n"/>
       <c r="D162" s="16" t="n"/>
       <c r="E162" s="21" t="n"/>
       <c r="F162" s="16" t="n"/>
@@ -38284,7 +39996,7 @@
     <row r="163">
       <c r="A163" s="15" t="n"/>
       <c r="B163" s="15" t="n"/>
-      <c r="C163" s="20" t="n"/>
+      <c r="C163" s="62" t="n"/>
       <c r="D163" s="16" t="n"/>
       <c r="E163" s="21" t="n"/>
       <c r="F163" s="16" t="n"/>
@@ -38329,7 +40041,7 @@
     <row r="164">
       <c r="A164" s="15" t="n"/>
       <c r="B164" s="15" t="n"/>
-      <c r="C164" s="20" t="n"/>
+      <c r="C164" s="62" t="n"/>
       <c r="D164" s="16" t="n"/>
       <c r="E164" s="21" t="n"/>
       <c r="F164" s="16" t="n"/>
@@ -38374,7 +40086,7 @@
     <row r="165">
       <c r="A165" s="15" t="n"/>
       <c r="B165" s="15" t="n"/>
-      <c r="C165" s="20" t="n"/>
+      <c r="C165" s="62" t="n"/>
       <c r="D165" s="16" t="n"/>
       <c r="E165" s="21" t="n"/>
       <c r="F165" s="16" t="n"/>
@@ -38419,7 +40131,7 @@
     <row r="166">
       <c r="A166" s="15" t="n"/>
       <c r="B166" s="15" t="n"/>
-      <c r="C166" s="20" t="n"/>
+      <c r="C166" s="62" t="n"/>
       <c r="D166" s="16" t="n"/>
       <c r="E166" s="21" t="n"/>
       <c r="F166" s="16" t="n"/>
@@ -38464,7 +40176,7 @@
     <row r="167">
       <c r="A167" s="15" t="n"/>
       <c r="B167" s="15" t="n"/>
-      <c r="C167" s="20" t="n"/>
+      <c r="C167" s="62" t="n"/>
       <c r="D167" s="16" t="n"/>
       <c r="E167" s="21" t="n"/>
       <c r="F167" s="16" t="n"/>
@@ -38509,7 +40221,7 @@
     <row r="168">
       <c r="A168" s="15" t="n"/>
       <c r="B168" s="15" t="n"/>
-      <c r="C168" s="20" t="n"/>
+      <c r="C168" s="62" t="n"/>
       <c r="D168" s="16" t="n"/>
       <c r="E168" s="21" t="n"/>
       <c r="F168" s="16" t="n"/>
@@ -38554,7 +40266,7 @@
     <row r="169">
       <c r="A169" s="15" t="n"/>
       <c r="B169" s="15" t="n"/>
-      <c r="C169" s="20" t="n"/>
+      <c r="C169" s="62" t="n"/>
       <c r="D169" s="16" t="n"/>
       <c r="E169" s="21" t="n"/>
       <c r="F169" s="16" t="n"/>
@@ -38599,7 +40311,7 @@
     <row r="170">
       <c r="A170" s="15" t="n"/>
       <c r="B170" s="15" t="n"/>
-      <c r="C170" s="20" t="n"/>
+      <c r="C170" s="62" t="n"/>
       <c r="D170" s="16" t="n"/>
       <c r="E170" s="21" t="n"/>
       <c r="F170" s="16" t="n"/>
@@ -38644,7 +40356,7 @@
     <row r="171">
       <c r="A171" s="15" t="n"/>
       <c r="B171" s="15" t="n"/>
-      <c r="C171" s="20" t="n"/>
+      <c r="C171" s="62" t="n"/>
       <c r="D171" s="16" t="n"/>
       <c r="E171" s="21" t="n"/>
       <c r="F171" s="16" t="n"/>
@@ -38689,7 +40401,7 @@
     <row r="172">
       <c r="A172" s="15" t="n"/>
       <c r="B172" s="15" t="n"/>
-      <c r="C172" s="20" t="n"/>
+      <c r="C172" s="62" t="n"/>
       <c r="D172" s="16" t="n"/>
       <c r="E172" s="21" t="n"/>
       <c r="F172" s="16" t="n"/>
@@ -38734,7 +40446,7 @@
     <row r="173">
       <c r="A173" s="15" t="n"/>
       <c r="B173" s="15" t="n"/>
-      <c r="C173" s="20" t="n"/>
+      <c r="C173" s="62" t="n"/>
       <c r="D173" s="16" t="n"/>
       <c r="E173" s="21" t="n"/>
       <c r="F173" s="16" t="n"/>
@@ -38779,7 +40491,7 @@
     <row r="174">
       <c r="A174" s="15" t="n"/>
       <c r="B174" s="15" t="n"/>
-      <c r="C174" s="20" t="n"/>
+      <c r="C174" s="62" t="n"/>
       <c r="D174" s="16" t="n"/>
       <c r="E174" s="21" t="n"/>
       <c r="F174" s="16" t="n"/>
@@ -38824,7 +40536,7 @@
     <row r="175">
       <c r="A175" s="15" t="n"/>
       <c r="B175" s="15" t="n"/>
-      <c r="C175" s="20" t="n"/>
+      <c r="C175" s="62" t="n"/>
       <c r="D175" s="16" t="n"/>
       <c r="E175" s="21" t="n"/>
       <c r="F175" s="16" t="n"/>
@@ -38869,7 +40581,7 @@
     <row r="176">
       <c r="A176" s="15" t="n"/>
       <c r="B176" s="15" t="n"/>
-      <c r="C176" s="20" t="n"/>
+      <c r="C176" s="62" t="n"/>
       <c r="D176" s="16" t="n"/>
       <c r="E176" s="21" t="n"/>
       <c r="F176" s="16" t="n"/>
@@ -38914,7 +40626,7 @@
     <row r="177">
       <c r="A177" s="15" t="n"/>
       <c r="B177" s="15" t="n"/>
-      <c r="C177" s="20" t="n"/>
+      <c r="C177" s="62" t="n"/>
       <c r="D177" s="16" t="n"/>
       <c r="E177" s="21" t="n"/>
       <c r="F177" s="16" t="n"/>
@@ -38959,7 +40671,7 @@
     <row r="178">
       <c r="A178" s="15" t="n"/>
       <c r="B178" s="15" t="n"/>
-      <c r="C178" s="20" t="n"/>
+      <c r="C178" s="62" t="n"/>
       <c r="D178" s="16" t="n"/>
       <c r="E178" s="21" t="n"/>
       <c r="F178" s="16" t="n"/>
@@ -39004,7 +40716,7 @@
     <row r="179">
       <c r="A179" s="15" t="n"/>
       <c r="B179" s="15" t="n"/>
-      <c r="C179" s="20" t="n"/>
+      <c r="C179" s="62" t="n"/>
       <c r="D179" s="16" t="n"/>
       <c r="E179" s="21" t="n"/>
       <c r="F179" s="16" t="n"/>
@@ -39049,7 +40761,7 @@
     <row r="180">
       <c r="A180" s="15" t="n"/>
       <c r="B180" s="15" t="n"/>
-      <c r="C180" s="20" t="n"/>
+      <c r="C180" s="62" t="n"/>
       <c r="D180" s="16" t="n"/>
       <c r="E180" s="21" t="n"/>
       <c r="F180" s="16" t="n"/>
@@ -39094,7 +40806,7 @@
     <row r="181">
       <c r="A181" s="15" t="n"/>
       <c r="B181" s="15" t="n"/>
-      <c r="C181" s="20" t="n"/>
+      <c r="C181" s="62" t="n"/>
       <c r="D181" s="16" t="n"/>
       <c r="E181" s="21" t="n"/>
       <c r="F181" s="16" t="n"/>
@@ -39139,7 +40851,7 @@
     <row r="182">
       <c r="A182" s="15" t="n"/>
       <c r="B182" s="15" t="n"/>
-      <c r="C182" s="20" t="n"/>
+      <c r="C182" s="62" t="n"/>
       <c r="D182" s="16" t="n"/>
       <c r="E182" s="21" t="n"/>
       <c r="F182" s="16" t="n"/>
@@ -39184,7 +40896,7 @@
     <row r="183">
       <c r="A183" s="15" t="n"/>
       <c r="B183" s="15" t="n"/>
-      <c r="C183" s="20" t="n"/>
+      <c r="C183" s="62" t="n"/>
       <c r="D183" s="16" t="n"/>
       <c r="E183" s="21" t="n"/>
       <c r="F183" s="16" t="n"/>
@@ -39229,7 +40941,7 @@
     <row r="184">
       <c r="A184" s="15" t="n"/>
       <c r="B184" s="15" t="n"/>
-      <c r="C184" s="20" t="n"/>
+      <c r="C184" s="62" t="n"/>
       <c r="D184" s="16" t="n"/>
       <c r="E184" s="21" t="n"/>
       <c r="F184" s="16" t="n"/>
@@ -39274,7 +40986,7 @@
     <row r="185">
       <c r="A185" s="15" t="n"/>
       <c r="B185" s="15" t="n"/>
-      <c r="C185" s="20" t="n"/>
+      <c r="C185" s="62" t="n"/>
       <c r="D185" s="16" t="n"/>
       <c r="E185" s="21" t="n"/>
       <c r="F185" s="16" t="n"/>
@@ -39319,7 +41031,7 @@
     <row r="186">
       <c r="A186" s="15" t="n"/>
       <c r="B186" s="15" t="n"/>
-      <c r="C186" s="20" t="n"/>
+      <c r="C186" s="62" t="n"/>
       <c r="D186" s="16" t="n"/>
       <c r="E186" s="21" t="n"/>
       <c r="F186" s="16" t="n"/>
@@ -39364,7 +41076,7 @@
     <row r="187">
       <c r="A187" s="15" t="n"/>
       <c r="B187" s="15" t="n"/>
-      <c r="C187" s="20" t="n"/>
+      <c r="C187" s="62" t="n"/>
       <c r="D187" s="16" t="n"/>
       <c r="E187" s="21" t="n"/>
       <c r="F187" s="16" t="n"/>
@@ -39409,7 +41121,7 @@
     <row r="188">
       <c r="A188" s="15" t="n"/>
       <c r="B188" s="15" t="n"/>
-      <c r="C188" s="20" t="n"/>
+      <c r="C188" s="62" t="n"/>
       <c r="D188" s="16" t="n"/>
       <c r="E188" s="21" t="n"/>
       <c r="F188" s="16" t="n"/>
@@ -39454,7 +41166,7 @@
     <row r="189">
       <c r="A189" s="15" t="n"/>
       <c r="B189" s="15" t="n"/>
-      <c r="C189" s="20" t="n"/>
+      <c r="C189" s="62" t="n"/>
       <c r="D189" s="16" t="n"/>
       <c r="E189" s="21" t="n"/>
       <c r="F189" s="16" t="n"/>
@@ -39499,7 +41211,7 @@
     <row r="190">
       <c r="A190" s="15" t="n"/>
       <c r="B190" s="15" t="n"/>
-      <c r="C190" s="20" t="n"/>
+      <c r="C190" s="62" t="n"/>
       <c r="D190" s="16" t="n"/>
       <c r="E190" s="21" t="n"/>
       <c r="F190" s="16" t="n"/>
@@ -39544,7 +41256,7 @@
     <row r="191">
       <c r="A191" s="15" t="n"/>
       <c r="B191" s="15" t="n"/>
-      <c r="C191" s="20" t="n"/>
+      <c r="C191" s="62" t="n"/>
       <c r="D191" s="16" t="n"/>
       <c r="E191" s="21" t="n"/>
       <c r="F191" s="16" t="n"/>
@@ -39589,7 +41301,7 @@
     <row r="192">
       <c r="A192" s="15" t="n"/>
       <c r="B192" s="15" t="n"/>
-      <c r="C192" s="20" t="n"/>
+      <c r="C192" s="62" t="n"/>
       <c r="D192" s="16" t="n"/>
       <c r="E192" s="21" t="n"/>
       <c r="F192" s="16" t="n"/>
@@ -39634,7 +41346,7 @@
     <row r="193">
       <c r="A193" s="15" t="n"/>
       <c r="B193" s="15" t="n"/>
-      <c r="C193" s="20" t="n"/>
+      <c r="C193" s="62" t="n"/>
       <c r="D193" s="16" t="n"/>
       <c r="E193" s="21" t="n"/>
       <c r="F193" s="16" t="n"/>
@@ -39679,7 +41391,7 @@
     <row r="194">
       <c r="A194" s="15" t="n"/>
       <c r="B194" s="15" t="n"/>
-      <c r="C194" s="20" t="n"/>
+      <c r="C194" s="62" t="n"/>
       <c r="D194" s="16" t="n"/>
       <c r="E194" s="21" t="n"/>
       <c r="F194" s="16" t="n"/>
@@ -39724,7 +41436,7 @@
     <row r="195">
       <c r="A195" s="15" t="n"/>
       <c r="B195" s="15" t="n"/>
-      <c r="C195" s="20" t="n"/>
+      <c r="C195" s="62" t="n"/>
       <c r="D195" s="16" t="n"/>
       <c r="E195" s="21" t="n"/>
       <c r="F195" s="16" t="n"/>
@@ -39769,7 +41481,7 @@
     <row r="196">
       <c r="A196" s="15" t="n"/>
       <c r="B196" s="15" t="n"/>
-      <c r="C196" s="20" t="n"/>
+      <c r="C196" s="62" t="n"/>
       <c r="D196" s="16" t="n"/>
       <c r="E196" s="21" t="n"/>
       <c r="F196" s="16" t="n"/>
@@ -39814,7 +41526,7 @@
     <row r="197">
       <c r="A197" s="15" t="n"/>
       <c r="B197" s="15" t="n"/>
-      <c r="C197" s="20" t="n"/>
+      <c r="C197" s="62" t="n"/>
       <c r="D197" s="16" t="n"/>
       <c r="E197" s="21" t="n"/>
       <c r="F197" s="16" t="n"/>
@@ -39859,7 +41571,7 @@
     <row r="198">
       <c r="A198" s="15" t="n"/>
       <c r="B198" s="15" t="n"/>
-      <c r="C198" s="20" t="n"/>
+      <c r="C198" s="62" t="n"/>
       <c r="D198" s="16" t="n"/>
       <c r="E198" s="21" t="n"/>
       <c r="F198" s="16" t="n"/>
@@ -39904,7 +41616,7 @@
     <row r="199">
       <c r="A199" s="15" t="n"/>
       <c r="B199" s="15" t="n"/>
-      <c r="C199" s="20" t="n"/>
+      <c r="C199" s="62" t="n"/>
       <c r="D199" s="16" t="n"/>
       <c r="E199" s="21" t="n"/>
       <c r="F199" s="16" t="n"/>
@@ -39949,7 +41661,7 @@
     <row r="200">
       <c r="A200" s="15" t="n"/>
       <c r="B200" s="15" t="n"/>
-      <c r="C200" s="20" t="n"/>
+      <c r="C200" s="62" t="n"/>
       <c r="D200" s="16" t="n"/>
       <c r="E200" s="21" t="n"/>
       <c r="F200" s="16" t="n"/>
@@ -39994,7 +41706,7 @@
     <row r="201">
       <c r="A201" s="15" t="n"/>
       <c r="B201" s="15" t="n"/>
-      <c r="C201" s="20" t="n"/>
+      <c r="C201" s="62" t="n"/>
       <c r="D201" s="16" t="n"/>
       <c r="E201" s="21" t="n"/>
       <c r="F201" s="16" t="n"/>
@@ -40039,7 +41751,7 @@
     <row r="202">
       <c r="A202" s="15" t="n"/>
       <c r="B202" s="15" t="n"/>
-      <c r="C202" s="20" t="n"/>
+      <c r="C202" s="62" t="n"/>
       <c r="D202" s="16" t="n"/>
       <c r="E202" s="21" t="n"/>
       <c r="F202" s="16" t="n"/>
@@ -40084,7 +41796,7 @@
     <row r="203">
       <c r="A203" s="15" t="n"/>
       <c r="B203" s="15" t="n"/>
-      <c r="C203" s="20" t="n"/>
+      <c r="C203" s="62" t="n"/>
       <c r="D203" s="16" t="n"/>
       <c r="E203" s="21" t="n"/>
       <c r="F203" s="16" t="n"/>
@@ -40129,7 +41841,7 @@
     <row r="204">
       <c r="A204" s="15" t="n"/>
       <c r="B204" s="15" t="n"/>
-      <c r="C204" s="20" t="n"/>
+      <c r="C204" s="62" t="n"/>
       <c r="D204" s="16" t="n"/>
       <c r="E204" s="21" t="n"/>
       <c r="F204" s="16" t="n"/>
@@ -40174,7 +41886,7 @@
     <row r="205">
       <c r="A205" s="15" t="n"/>
       <c r="B205" s="15" t="n"/>
-      <c r="C205" s="20" t="n"/>
+      <c r="C205" s="62" t="n"/>
       <c r="D205" s="16" t="n"/>
       <c r="E205" s="21" t="n"/>
       <c r="F205" s="16" t="n"/>
@@ -40219,7 +41931,7 @@
     <row r="206">
       <c r="A206" s="15" t="n"/>
       <c r="B206" s="15" t="n"/>
-      <c r="C206" s="20" t="n"/>
+      <c r="C206" s="62" t="n"/>
       <c r="D206" s="16" t="n"/>
       <c r="E206" s="21" t="n"/>
       <c r="F206" s="16" t="n"/>
@@ -40264,7 +41976,7 @@
     <row r="207">
       <c r="A207" s="15" t="n"/>
       <c r="B207" s="15" t="n"/>
-      <c r="C207" s="20" t="n"/>
+      <c r="C207" s="62" t="n"/>
       <c r="D207" s="16" t="n"/>
       <c r="E207" s="21" t="n"/>
       <c r="F207" s="16" t="n"/>
@@ -40309,7 +42021,7 @@
     <row r="208">
       <c r="A208" s="15" t="n"/>
       <c r="B208" s="15" t="n"/>
-      <c r="C208" s="20" t="n"/>
+      <c r="C208" s="62" t="n"/>
       <c r="D208" s="16" t="n"/>
       <c r="E208" s="21" t="n"/>
       <c r="F208" s="16" t="n"/>
@@ -40354,7 +42066,7 @@
     <row r="209">
       <c r="A209" s="15" t="n"/>
       <c r="B209" s="15" t="n"/>
-      <c r="C209" s="20" t="n"/>
+      <c r="C209" s="62" t="n"/>
       <c r="D209" s="16" t="n"/>
       <c r="E209" s="21" t="n"/>
       <c r="F209" s="16" t="n"/>
@@ -40399,7 +42111,7 @@
     <row r="210">
       <c r="A210" s="15" t="n"/>
       <c r="B210" s="15" t="n"/>
-      <c r="C210" s="20" t="n"/>
+      <c r="C210" s="62" t="n"/>
       <c r="D210" s="16" t="n"/>
       <c r="E210" s="21" t="n"/>
       <c r="F210" s="16" t="n"/>
@@ -40444,7 +42156,7 @@
     <row r="211">
       <c r="A211" s="15" t="n"/>
       <c r="B211" s="15" t="n"/>
-      <c r="C211" s="20" t="n"/>
+      <c r="C211" s="62" t="n"/>
       <c r="D211" s="16" t="n"/>
       <c r="E211" s="21" t="n"/>
       <c r="F211" s="16" t="n"/>
@@ -40489,7 +42201,7 @@
     <row r="212">
       <c r="A212" s="15" t="n"/>
       <c r="B212" s="15" t="n"/>
-      <c r="C212" s="20" t="n"/>
+      <c r="C212" s="62" t="n"/>
       <c r="D212" s="16" t="n"/>
       <c r="E212" s="21" t="n"/>
       <c r="F212" s="16" t="n"/>
@@ -40534,7 +42246,7 @@
     <row r="213">
       <c r="A213" s="15" t="n"/>
       <c r="B213" s="15" t="n"/>
-      <c r="C213" s="20" t="n"/>
+      <c r="C213" s="62" t="n"/>
       <c r="D213" s="16" t="n"/>
       <c r="E213" s="21" t="n"/>
       <c r="F213" s="16" t="n"/>
@@ -40579,7 +42291,7 @@
     <row r="214">
       <c r="A214" s="15" t="n"/>
       <c r="B214" s="15" t="n"/>
-      <c r="C214" s="20" t="n"/>
+      <c r="C214" s="62" t="n"/>
       <c r="D214" s="16" t="n"/>
       <c r="E214" s="21" t="n"/>
       <c r="F214" s="16" t="n"/>
@@ -40624,7 +42336,7 @@
     <row r="215">
       <c r="A215" s="15" t="n"/>
       <c r="B215" s="15" t="n"/>
-      <c r="C215" s="20" t="n"/>
+      <c r="C215" s="62" t="n"/>
       <c r="D215" s="16" t="n"/>
       <c r="E215" s="21" t="n"/>
       <c r="F215" s="16" t="n"/>
@@ -40669,7 +42381,7 @@
     <row r="216">
       <c r="A216" s="15" t="n"/>
       <c r="B216" s="15" t="n"/>
-      <c r="C216" s="20" t="n"/>
+      <c r="C216" s="62" t="n"/>
       <c r="D216" s="16" t="n"/>
       <c r="E216" s="21" t="n"/>
       <c r="F216" s="16" t="n"/>
@@ -40714,7 +42426,7 @@
     <row r="217">
       <c r="A217" s="15" t="n"/>
       <c r="B217" s="15" t="n"/>
-      <c r="C217" s="20" t="n"/>
+      <c r="C217" s="62" t="n"/>
       <c r="D217" s="16" t="n"/>
       <c r="E217" s="21" t="n"/>
       <c r="F217" s="16" t="n"/>
@@ -40759,7 +42471,7 @@
     <row r="218">
       <c r="A218" s="15" t="n"/>
       <c r="B218" s="15" t="n"/>
-      <c r="C218" s="20" t="n"/>
+      <c r="C218" s="62" t="n"/>
       <c r="D218" s="16" t="n"/>
       <c r="E218" s="21" t="n"/>
       <c r="F218" s="16" t="n"/>
@@ -40804,7 +42516,7 @@
     <row r="219">
       <c r="A219" s="15" t="n"/>
       <c r="B219" s="15" t="n"/>
-      <c r="C219" s="20" t="n"/>
+      <c r="C219" s="62" t="n"/>
       <c r="D219" s="16" t="n"/>
       <c r="E219" s="21" t="n"/>
       <c r="F219" s="16" t="n"/>
@@ -40849,7 +42561,7 @@
     <row r="220">
       <c r="A220" s="15" t="n"/>
       <c r="B220" s="15" t="n"/>
-      <c r="C220" s="20" t="n"/>
+      <c r="C220" s="62" t="n"/>
       <c r="D220" s="16" t="n"/>
       <c r="E220" s="21" t="n"/>
       <c r="F220" s="16" t="n"/>
@@ -40894,7 +42606,7 @@
     <row r="221">
       <c r="A221" s="15" t="n"/>
       <c r="B221" s="15" t="n"/>
-      <c r="C221" s="20" t="n"/>
+      <c r="C221" s="62" t="n"/>
       <c r="D221" s="16" t="n"/>
       <c r="E221" s="21" t="n"/>
       <c r="F221" s="16" t="n"/>
@@ -40939,7 +42651,7 @@
     <row r="222">
       <c r="A222" s="15" t="n"/>
       <c r="B222" s="15" t="n"/>
-      <c r="C222" s="20" t="n"/>
+      <c r="C222" s="62" t="n"/>
       <c r="D222" s="16" t="n"/>
       <c r="E222" s="21" t="n"/>
       <c r="F222" s="16" t="n"/>
@@ -40984,7 +42696,7 @@
     <row r="223">
       <c r="A223" s="15" t="n"/>
       <c r="B223" s="15" t="n"/>
-      <c r="C223" s="20" t="n"/>
+      <c r="C223" s="62" t="n"/>
       <c r="D223" s="16" t="n"/>
       <c r="E223" s="21" t="n"/>
       <c r="F223" s="16" t="n"/>
@@ -41029,7 +42741,7 @@
     <row r="224">
       <c r="A224" s="15" t="n"/>
       <c r="B224" s="15" t="n"/>
-      <c r="C224" s="20" t="n"/>
+      <c r="C224" s="62" t="n"/>
       <c r="D224" s="16" t="n"/>
       <c r="E224" s="21" t="n"/>
       <c r="F224" s="16" t="n"/>
@@ -41074,7 +42786,7 @@
     <row r="225">
       <c r="A225" s="15" t="n"/>
       <c r="B225" s="15" t="n"/>
-      <c r="C225" s="20" t="n"/>
+      <c r="C225" s="62" t="n"/>
       <c r="D225" s="16" t="n"/>
       <c r="E225" s="21" t="n"/>
       <c r="F225" s="16" t="n"/>
@@ -41119,7 +42831,7 @@
     <row r="226">
       <c r="A226" s="15" t="n"/>
       <c r="B226" s="15" t="n"/>
-      <c r="C226" s="20" t="n"/>
+      <c r="C226" s="62" t="n"/>
       <c r="D226" s="16" t="n"/>
       <c r="E226" s="21" t="n"/>
       <c r="F226" s="16" t="n"/>
@@ -41164,7 +42876,7 @@
     <row r="227">
       <c r="A227" s="15" t="n"/>
       <c r="B227" s="15" t="n"/>
-      <c r="C227" s="20" t="n"/>
+      <c r="C227" s="62" t="n"/>
       <c r="D227" s="16" t="n"/>
       <c r="E227" s="21" t="n"/>
       <c r="F227" s="16" t="n"/>
@@ -41209,7 +42921,7 @@
     <row r="228">
       <c r="A228" s="15" t="n"/>
       <c r="B228" s="15" t="n"/>
-      <c r="C228" s="20" t="n"/>
+      <c r="C228" s="62" t="n"/>
       <c r="D228" s="16" t="n"/>
       <c r="E228" s="21" t="n"/>
       <c r="F228" s="16" t="n"/>
@@ -41254,7 +42966,7 @@
     <row r="229">
       <c r="A229" s="15" t="n"/>
       <c r="B229" s="15" t="n"/>
-      <c r="C229" s="20" t="n"/>
+      <c r="C229" s="62" t="n"/>
       <c r="D229" s="16" t="n"/>
       <c r="E229" s="21" t="n"/>
       <c r="F229" s="16" t="n"/>
@@ -41299,7 +43011,7 @@
     <row r="230">
       <c r="A230" s="15" t="n"/>
       <c r="B230" s="15" t="n"/>
-      <c r="C230" s="20" t="n"/>
+      <c r="C230" s="62" t="n"/>
       <c r="D230" s="16" t="n"/>
       <c r="E230" s="21" t="n"/>
       <c r="F230" s="16" t="n"/>
@@ -41344,7 +43056,7 @@
     <row r="231">
       <c r="A231" s="15" t="n"/>
       <c r="B231" s="15" t="n"/>
-      <c r="C231" s="20" t="n"/>
+      <c r="C231" s="62" t="n"/>
       <c r="D231" s="16" t="n"/>
       <c r="E231" s="21" t="n"/>
       <c r="F231" s="16" t="n"/>
@@ -41389,7 +43101,7 @@
     <row r="232">
       <c r="A232" s="15" t="n"/>
       <c r="B232" s="15" t="n"/>
-      <c r="C232" s="20" t="n"/>
+      <c r="C232" s="62" t="n"/>
       <c r="D232" s="16" t="n"/>
       <c r="E232" s="21" t="n"/>
       <c r="F232" s="16" t="n"/>
@@ -41434,7 +43146,7 @@
     <row r="233">
       <c r="A233" s="15" t="n"/>
       <c r="B233" s="15" t="n"/>
-      <c r="C233" s="20" t="n"/>
+      <c r="C233" s="62" t="n"/>
       <c r="D233" s="16" t="n"/>
       <c r="E233" s="21" t="n"/>
       <c r="F233" s="16" t="n"/>
@@ -41479,7 +43191,7 @@
     <row r="234">
       <c r="A234" s="15" t="n"/>
       <c r="B234" s="15" t="n"/>
-      <c r="C234" s="20" t="n"/>
+      <c r="C234" s="62" t="n"/>
       <c r="D234" s="16" t="n"/>
       <c r="E234" s="21" t="n"/>
       <c r="F234" s="16" t="n"/>
@@ -41524,7 +43236,7 @@
     <row r="235">
       <c r="A235" s="15" t="n"/>
       <c r="B235" s="15" t="n"/>
-      <c r="C235" s="20" t="n"/>
+      <c r="C235" s="62" t="n"/>
       <c r="D235" s="16" t="n"/>
       <c r="E235" s="21" t="n"/>
       <c r="F235" s="16" t="n"/>
@@ -41569,7 +43281,7 @@
     <row r="236">
       <c r="A236" s="15" t="n"/>
       <c r="B236" s="15" t="n"/>
-      <c r="C236" s="20" t="n"/>
+      <c r="C236" s="62" t="n"/>
       <c r="D236" s="16" t="n"/>
       <c r="E236" s="21" t="n"/>
       <c r="F236" s="16" t="n"/>
@@ -41614,7 +43326,7 @@
     <row r="237">
       <c r="A237" s="15" t="n"/>
       <c r="B237" s="15" t="n"/>
-      <c r="C237" s="20" t="n"/>
+      <c r="C237" s="62" t="n"/>
       <c r="D237" s="16" t="n"/>
       <c r="E237" s="21" t="n"/>
       <c r="F237" s="16" t="n"/>
@@ -41659,7 +43371,7 @@
     <row r="238">
       <c r="A238" s="15" t="n"/>
       <c r="B238" s="15" t="n"/>
-      <c r="C238" s="20" t="n"/>
+      <c r="C238" s="62" t="n"/>
       <c r="D238" s="16" t="n"/>
       <c r="E238" s="21" t="n"/>
       <c r="F238" s="16" t="n"/>
@@ -41704,7 +43416,7 @@
     <row r="239">
       <c r="A239" s="15" t="n"/>
       <c r="B239" s="15" t="n"/>
-      <c r="C239" s="20" t="n"/>
+      <c r="C239" s="62" t="n"/>
       <c r="D239" s="16" t="n"/>
       <c r="E239" s="21" t="n"/>
       <c r="F239" s="16" t="n"/>
@@ -41749,7 +43461,7 @@
     <row r="240">
       <c r="A240" s="15" t="n"/>
       <c r="B240" s="15" t="n"/>
-      <c r="C240" s="20" t="n"/>
+      <c r="C240" s="62" t="n"/>
       <c r="D240" s="16" t="n"/>
       <c r="E240" s="21" t="n"/>
       <c r="F240" s="16" t="n"/>
@@ -41794,7 +43506,7 @@
     <row r="241">
       <c r="A241" s="15" t="n"/>
       <c r="B241" s="15" t="n"/>
-      <c r="C241" s="20" t="n"/>
+      <c r="C241" s="62" t="n"/>
       <c r="D241" s="16" t="n"/>
       <c r="E241" s="21" t="n"/>
       <c r="F241" s="16" t="n"/>
@@ -41839,7 +43551,7 @@
     <row r="242">
       <c r="A242" s="15" t="n"/>
       <c r="B242" s="15" t="n"/>
-      <c r="C242" s="20" t="n"/>
+      <c r="C242" s="62" t="n"/>
       <c r="D242" s="16" t="n"/>
       <c r="E242" s="21" t="n"/>
       <c r="F242" s="16" t="n"/>
@@ -41884,7 +43596,7 @@
     <row r="243">
       <c r="A243" s="15" t="n"/>
       <c r="B243" s="15" t="n"/>
-      <c r="C243" s="20" t="n"/>
+      <c r="C243" s="62" t="n"/>
       <c r="D243" s="16" t="n"/>
       <c r="E243" s="21" t="n"/>
       <c r="F243" s="16" t="n"/>
@@ -41929,7 +43641,7 @@
     <row r="244">
       <c r="A244" s="15" t="n"/>
       <c r="B244" s="15" t="n"/>
-      <c r="C244" s="20" t="n"/>
+      <c r="C244" s="62" t="n"/>
       <c r="D244" s="16" t="n"/>
       <c r="E244" s="21" t="n"/>
       <c r="F244" s="16" t="n"/>
@@ -41974,7 +43686,7 @@
     <row r="245">
       <c r="A245" s="15" t="n"/>
       <c r="B245" s="15" t="n"/>
-      <c r="C245" s="20" t="n"/>
+      <c r="C245" s="62" t="n"/>
       <c r="D245" s="16" t="n"/>
       <c r="E245" s="21" t="n"/>
       <c r="F245" s="16" t="n"/>
@@ -42019,7 +43731,7 @@
     <row r="246">
       <c r="A246" s="15" t="n"/>
       <c r="B246" s="15" t="n"/>
-      <c r="C246" s="20" t="n"/>
+      <c r="C246" s="62" t="n"/>
       <c r="D246" s="16" t="n"/>
       <c r="E246" s="21" t="n"/>
       <c r="F246" s="16" t="n"/>
@@ -42064,7 +43776,7 @@
     <row r="247">
       <c r="A247" s="15" t="n"/>
       <c r="B247" s="15" t="n"/>
-      <c r="C247" s="20" t="n"/>
+      <c r="C247" s="62" t="n"/>
       <c r="D247" s="16" t="n"/>
       <c r="E247" s="21" t="n"/>
       <c r="F247" s="16" t="n"/>
@@ -42109,7 +43821,7 @@
     <row r="248">
       <c r="A248" s="15" t="n"/>
       <c r="B248" s="15" t="n"/>
-      <c r="C248" s="20" t="n"/>
+      <c r="C248" s="62" t="n"/>
       <c r="D248" s="16" t="n"/>
       <c r="E248" s="21" t="n"/>
       <c r="F248" s="16" t="n"/>
@@ -42154,7 +43866,7 @@
     <row r="249">
       <c r="A249" s="15" t="n"/>
       <c r="B249" s="15" t="n"/>
-      <c r="C249" s="20" t="n"/>
+      <c r="C249" s="62" t="n"/>
       <c r="D249" s="16" t="n"/>
       <c r="E249" s="21" t="n"/>
       <c r="F249" s="16" t="n"/>
@@ -42199,7 +43911,7 @@
     <row r="250">
       <c r="A250" s="15" t="n"/>
       <c r="B250" s="15" t="n"/>
-      <c r="C250" s="20" t="n"/>
+      <c r="C250" s="62" t="n"/>
       <c r="D250" s="16" t="n"/>
       <c r="E250" s="21" t="n"/>
       <c r="F250" s="16" t="n"/>
@@ -42244,7 +43956,7 @@
     <row r="251">
       <c r="A251" s="15" t="n"/>
       <c r="B251" s="15" t="n"/>
-      <c r="C251" s="20" t="n"/>
+      <c r="C251" s="62" t="n"/>
       <c r="D251" s="16" t="n"/>
       <c r="E251" s="21" t="n"/>
       <c r="F251" s="16" t="n"/>
@@ -42289,7 +44001,7 @@
     <row r="252">
       <c r="A252" s="15" t="n"/>
       <c r="B252" s="15" t="n"/>
-      <c r="C252" s="20" t="n"/>
+      <c r="C252" s="62" t="n"/>
       <c r="D252" s="16" t="n"/>
       <c r="E252" s="21" t="n"/>
       <c r="F252" s="16" t="n"/>
@@ -42334,7 +44046,7 @@
     <row r="253">
       <c r="A253" s="15" t="n"/>
       <c r="B253" s="15" t="n"/>
-      <c r="C253" s="20" t="n"/>
+      <c r="C253" s="62" t="n"/>
       <c r="D253" s="16" t="n"/>
       <c r="E253" s="21" t="n"/>
       <c r="F253" s="16" t="n"/>
@@ -42379,7 +44091,7 @@
     <row r="254">
       <c r="A254" s="15" t="n"/>
       <c r="B254" s="15" t="n"/>
-      <c r="C254" s="20" t="n"/>
+      <c r="C254" s="62" t="n"/>
       <c r="D254" s="16" t="n"/>
       <c r="E254" s="21" t="n"/>
       <c r="F254" s="16" t="n"/>
@@ -42424,7 +44136,7 @@
     <row r="255">
       <c r="A255" s="15" t="n"/>
       <c r="B255" s="15" t="n"/>
-      <c r="C255" s="20" t="n"/>
+      <c r="C255" s="62" t="n"/>
       <c r="D255" s="16" t="n"/>
       <c r="E255" s="21" t="n"/>
       <c r="F255" s="16" t="n"/>
@@ -42525,7 +44237,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -42549,21 +44261,6 @@
           <t>DONEM ANALIZ — GES Üretim &amp; Performans Takibi</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -42571,17 +44268,6 @@
           <t>12 aylık sezonsallık — üretim ve PR zinciri (S03)</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
@@ -43175,7 +44861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -43196,17 +44882,6 @@
           <t>HESAP — GES Üretim &amp; Performans Takibi</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -43214,15 +44889,6 @@
           <t>Hesap motoru — ≥40 adım; sabitler AYARLAR'dan</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
@@ -44379,7 +46045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -44401,23 +46067,6 @@
           <t>PANO — GES Üretim &amp; Performans Takibi</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -44425,19 +46074,6 @@
           <t>Karar panosu — PR, kayıp, alarm, sezonsal trend</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
@@ -44966,1063 +46602,4 @@
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000B3D2E"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ALARMLAR — GES Üretim &amp; Performans Takibi</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Alarm listesi — varlık + eşik + süre (S05)</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Varlık</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Alarm</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>Eşik</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>Süre / Tarih</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>PR Ort</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="inlineStr">
-        <is>
-          <t>Sağlık Skor</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>GES-00001</t>
-        </is>
-      </c>
-      <c r="B6" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A6,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C6" s="24">
-        <f>IFERROR(ABS(E6-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E6" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>GES-00002</t>
-        </is>
-      </c>
-      <c r="B7" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A7,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C7" s="24">
-        <f>IFERROR(ABS(E7-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="32">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E7" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>GES-00003</t>
-        </is>
-      </c>
-      <c r="B8" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A8,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C8" s="24">
-        <f>IFERROR(ABS(E8-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="32">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E8" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>GES-00004</t>
-        </is>
-      </c>
-      <c r="B9" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A9,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C9" s="24">
-        <f>IFERROR(ABS(E9-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="32">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E9" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>GES-00005</t>
-        </is>
-      </c>
-      <c r="B10" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A10,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C10" s="24">
-        <f>IFERROR(ABS(E10-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E10" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>GES-00006</t>
-        </is>
-      </c>
-      <c r="B11" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A11,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C11" s="24">
-        <f>IFERROR(ABS(E11-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="32">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E11" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>GES-00007</t>
-        </is>
-      </c>
-      <c r="B12" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A12,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C12" s="24">
-        <f>IFERROR(ABS(E12-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E12" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>GES-00008</t>
-        </is>
-      </c>
-      <c r="B13" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A13,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C13" s="24">
-        <f>IFERROR(ABS(E13-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="32">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E13" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Alarm Özeti</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>gup_alarmListesi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Toplam Alarm Satır</t>
-        </is>
-      </c>
-      <c r="B18" s="23">
-        <f>COUNTIF(B6:B13,"ALARM")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A1:N1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6:B13">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
-      <formula>"ALARM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
-      <formula>"YOK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
-    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="8">
-    <dataValidation sqref="A6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000B3D2E"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RAPOR — GES Üretim &amp; Performans Takibi</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Dönemsel yönetim raporu — yazdırılabilir kanıt</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Ürün</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>GES Üretim &amp; Performans Takibi</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Sürüm</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Rapor Tarihi</t>
-        </is>
-      </c>
-      <c r="B7" s="32">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Firma</t>
-        </is>
-      </c>
-      <c r="B8" s="7">
-        <f>gup_firmaUnvan</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>KARAR</t>
-        </is>
-      </c>
-      <c r="B10" s="34">
-        <f>gup_kararKapi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>PR Oranı</t>
-        </is>
-      </c>
-      <c r="B11" s="24">
-        <f>gup_prOrani</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Üretim kWh</t>
-        </is>
-      </c>
-      <c r="B12" s="26">
-        <f>gup_toplamUretim</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Kayıp kWh</t>
-        </is>
-      </c>
-      <c r="B13" s="26">
-        <f>gup_toplamKayip</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Sağlık Skor</t>
-        </is>
-      </c>
-      <c r="B14" s="23">
-        <f>gup_saglikSkor</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Alarm Adet</t>
-        </is>
-      </c>
-      <c r="B15" s="23">
-        <f>gup_alarmAdet</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>Kalem</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Teorik üretim</t>
-        </is>
-      </c>
-      <c r="B18" s="26">
-        <f>gup_teorikUretim</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Kayıp payı</t>
-        </is>
-      </c>
-      <c r="B19" s="24">
-        <f>gup_kayipPay</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Günlük PR ort</t>
-        </is>
-      </c>
-      <c r="B20" s="24">
-        <f>gup_gunlukPrOrt</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Kalite skor</t>
-        </is>
-      </c>
-      <c r="B21" s="23">
-        <f>gup_kaliteSkor</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>Varsayımlar</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>PR = üretim / (ışınım × kapasite). Eşikler AYARLAR'dan gelir. Karar destek çıktısıdır; mali veya mühendislik tavsiyesi değildir. IEC 61724 referanslı performans oranı yaklaşımıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>İmza — GES İşletme Müdürü</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>________________</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>İmza — CFO / Varlık Yöneticisi</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>________________</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>SHA notu: sevk paketinde SHA-256 yer alır | 1.0.0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
-    <mergeCell ref="A25:F26"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:J3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B10">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
-      <formula>"UYGUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
-      <formula>"DİKKAT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
-      <formula>"KRİTİK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
-      <formula>"VERİ YOK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
-    <cfRule type="cellIs" priority="10" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
-    <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="cellIs" priority="14" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="cellIs" priority="16" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Firma" error="Geçersiz" promptTitle="Firma" prompt="Firma unvanı (AYARLAR'dan)" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-      <formula2>80</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LGES Üretim &amp; Performans Takibi | Rapor | 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LGES Üretim &amp; Performans Takibi | Rapor | 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000B3D2E"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KONTROLLER — GES Üretim &amp; Performans Takibi</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Canlı sağlık kontrolleri — formülle</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Kontrol</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Sonuç</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Dolu kayıt &gt; 0</t>
-        </is>
-      </c>
-      <c r="B6" s="7">
-        <f>IF(gup_doluKayit&gt;0,"GEÇTİ","KALDI")</f>
-        <v/>
-      </c>
-      <c r="C6" s="7">
-        <f>gup_doluKayit</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Yetim kayıt = 0</t>
-        </is>
-      </c>
-      <c r="B7" s="7">
-        <f>IF(gup_yetimAdet=0,"GEÇTİ","UYARI")</f>
-        <v/>
-      </c>
-      <c r="C7" s="7">
-        <f>gup_yetimAdet</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>PR hesaplı</t>
-        </is>
-      </c>
-      <c r="B8" s="7">
-        <f>IF(gup_prOrani&gt;=0,"GEÇTİ","KALDI")</f>
-        <v/>
-      </c>
-      <c r="C8" s="7">
-        <f>gup_prOrani</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Sağlık skor formül</t>
-        </is>
-      </c>
-      <c r="B9" s="7">
-        <f>IF(gup_saglikSkor&gt;=0,"GEÇTİ","KALDI")</f>
-        <v/>
-      </c>
-      <c r="C9" s="7">
-        <f>gup_saglikSkor</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Alarm listesi</t>
-        </is>
-      </c>
-      <c r="B10" s="7">
-        <f>IF(gup_alarmAdet&gt;=0,"GEÇTİ","KALDI")</f>
-        <v/>
-      </c>
-      <c r="C10" s="7">
-        <f>gup_alarmAdet</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Karar dolu</t>
-        </is>
-      </c>
-      <c r="B11" s="7">
-        <f>IF(gup_kararKapi&lt;&gt;"","GEÇTİ","KALDI")</f>
-        <v/>
-      </c>
-      <c r="C11" s="7">
-        <f>gup_kararKapi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>12 ay sezonsal</t>
-        </is>
-      </c>
-      <c r="B12" s="7">
-        <f>IF(DONEM_ANALIZ!B22&gt;=0,"GEÇTİ","KALDI")</f>
-        <v/>
-      </c>
-      <c r="C12" s="7">
-        <f>DONEM_ANALIZ!B22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Kalite skor</t>
-        </is>
-      </c>
-      <c r="B13" s="7">
-        <f>IF(gup_kaliteSkor&gt;=0,"GEÇTİ","KALDI")</f>
-        <v/>
-      </c>
-      <c r="C13" s="7">
-        <f>gup_kaliteSkor</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Tornado</t>
-        </is>
-      </c>
-      <c r="B14" s="7">
-        <f>IF(gup_tornadoZirve&gt;=0,"GEÇTİ","KALDI")</f>
-        <v/>
-      </c>
-      <c r="C14" s="7">
-        <f>gup_tornadoZirve</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>P90</t>
-        </is>
-      </c>
-      <c r="B15" s="7">
-        <f>IF(gup_yuzdelikP90&gt;=0,"GEÇTİ","KALDI")</f>
-        <v/>
-      </c>
-      <c r="C15" s="7">
-        <f>gup_yuzdelikP90</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:J3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6:B15">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
-      <formula>"GEÇTİ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"KALDI"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
-      <formula>"UYARI"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/EXCELARSIV_PRODUCTS/ges-uretim-performans/GesUretimPerformans.xlsx
+++ b/EXCELARSIV_PRODUCTS/ges-uretim-performans/GesUretimPerformans.xlsx
@@ -7,22 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARLIKLAR" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUNLUK_GIRIS" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DONEM_ANALIZ" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HESAP" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALARMLAR" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="16" state="hidden" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARLIKLAR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUNLUK_GIRIS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DONEM_ANALIZ" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HESAP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALARMLAR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="raporTarihi">AYARLAR!$B$6</definedName>
@@ -86,8 +85,7 @@
     <definedName name="ListeEvetHayir">LISTELER!$A$7:$A$8</definedName>
     <definedName name="ListeKayipTuru">LISTELER!$C$7:$C$12</definedName>
     <definedName name="ListeSantralTipi">LISTELER!$E$7:$E$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'PANO'!$A$1:$N$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'RAPOR'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'RAPOR'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -95,15 +93,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="67">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -305,8 +304,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -361,8 +542,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -385,11 +632,100 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -554,6 +890,163 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="56" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="55" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="55" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="56" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="55" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="55" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="57" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -763,88 +1256,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Kayıp Adet</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$23:$A$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$23:$B$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
@@ -927,542 +1338,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Kayıp Türü Dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$23:$A$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$23:$B$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Senaryo Karşılaştırma</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$23:$D$25</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$23:$E$25</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Haftalık Üretim Trend</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!H22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'PANO'!$G$23:$G$30</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$H$23:$H$30</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Aylık PR</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!K22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$J$23:$J$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$K$23:$K$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Kayıp Payı (tekrar)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$23:$A$25</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$23:$B$25</f>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Senaryo vs Baz</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$23:$D$25</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$23:$E$25</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Üretim Trend (kısa)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!H22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'PANO'!$G$23:$G$28</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$H$23:$H$28</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -20244,9 +20119,54 @@
     <author>ExcelArşiv</author>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Karar kapısı | Neden önemli: Boş dosyada VERİ YOK | Doğru kullanım: Otomatik | Örnek: UYGUN | Risk: Elle müdahale yok</t>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>Tanım: Seçim | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: EVET/HAYIR | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0">
+      <text>
+        <t>Tanım: Tip | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Santral tipi | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>Tanım: Seçim | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: EVET/HAYIR | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>Tanım: Tip | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Santral tipi | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0" shapeId="0">
+      <text>
+        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0">
+      <text>
+        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0" shapeId="0">
+      <text>
+        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
       </text>
     </comment>
   </commentList>
@@ -20254,66 +20174,6 @@
 </file>
 
 <file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>ExcelArşiv</author>
-  </authors>
-  <commentList>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Seçim | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: EVET/HAYIR | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
-      </text>
-    </comment>
-    <comment ref="C7" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Tip | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Santral tipi | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
-      </text>
-    </comment>
-    <comment ref="A8" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Seçim | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: EVET/HAYIR | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Tip | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Santral tipi | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
-      </text>
-    </comment>
-    <comment ref="C9" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
-      </text>
-    </comment>
-    <comment ref="C10" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: Kayıp | Neden önemli: GES PR ve kayıp analizini etkiler | Doğru kullanım: Kayıp türü | Örnek: hücredeki örnek değere bakın | Risk: Yanlış giriş hatalı karar üretir</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>ExcelArşiv</author>
@@ -20479,187 +20339,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>61</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="5" name="Chart 5"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>61</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="6" name="Chart 6"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="7" name="Chart 7"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="8" name="Chart 8"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21027,792 +20706,581 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="37" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — GES URETIM PERFORMANS YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="38" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="65" t="inlineStr">
+        <is>
+          <t>GES URETIM PERFORMANS — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="66" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="67" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="68" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="69" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="70" t="n"/>
+      <c r="D5" s="71" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="72" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="70" t="n"/>
+      <c r="G5" s="73" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="69" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="70" t="n"/>
+      <c r="J5" s="74" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="75" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="70" t="n"/>
+      <c r="M5" s="71" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
-        </is>
-      </c>
-      <c r="D6" s="39" t="inlineStr">
-        <is>
-          <t>OPERASYONEL KÂR MARJI</t>
-        </is>
-      </c>
-      <c r="F6" s="39" t="inlineStr">
-        <is>
-          <t>SİSTEM VE RİSK DENETİMİ</t>
-        </is>
-      </c>
-      <c r="H6" s="40" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="76" t="n"/>
+      <c r="C6" s="70" t="n"/>
+      <c r="D6" s="70" t="n"/>
+      <c r="E6" s="77" t="n"/>
+      <c r="F6" s="70" t="n"/>
+      <c r="G6" s="70" t="n"/>
+      <c r="H6" s="76" t="n"/>
+      <c r="I6" s="70" t="n"/>
+      <c r="J6" s="70" t="n"/>
+      <c r="K6" s="78" t="n"/>
+      <c r="L6" s="70" t="n"/>
+      <c r="M6" s="70" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>₺ 18.750.000</t>
-        </is>
-      </c>
-      <c r="D7" s="41" t="inlineStr">
-        <is>
-          <t>% 26,5</t>
-        </is>
-      </c>
-      <c r="F7" s="42" t="inlineStr">
-        <is>
-          <t>KUSURSUZ (0 HATA)</t>
-        </is>
-      </c>
-      <c r="H7" s="43" t="inlineStr">
-        <is>
-          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="79" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="70" t="n"/>
+      <c r="D7" s="70" t="n"/>
+      <c r="E7" s="80" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="70" t="n"/>
+      <c r="G7" s="70" t="n"/>
+      <c r="H7" s="79" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="70" t="n"/>
+      <c r="J7" s="70" t="n"/>
+      <c r="K7" s="81" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="70" t="n"/>
+      <c r="M7" s="70" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="76" t="n"/>
+      <c r="C8" s="70" t="n"/>
+      <c r="D8" s="70" t="n"/>
+      <c r="E8" s="77" t="n"/>
+      <c r="F8" s="70" t="n"/>
+      <c r="G8" s="70" t="n"/>
+      <c r="H8" s="76" t="n"/>
+      <c r="I8" s="70" t="n"/>
+      <c r="J8" s="70" t="n"/>
+      <c r="K8" s="78" t="n"/>
+      <c r="L8" s="70" t="n"/>
+      <c r="M8" s="70" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="44" t="inlineStr">
-        <is>
-          <t>Model Güvenilirlik Skoru: 98/100</t>
-        </is>
-      </c>
-      <c r="D9" s="45" t="inlineStr">
-        <is>
-          <t>Yıllıklandırılmış Büyüme: +% 24</t>
-        </is>
-      </c>
-      <c r="F9" s="46" t="inlineStr">
-        <is>
-          <t>60+ Nokta Bağımsız Audit: PASS</t>
+      <c r="B9" s="82" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="70" t="n"/>
+      <c r="D9" s="70" t="n"/>
+      <c r="E9" s="83" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="70" t="n"/>
+      <c r="G9" s="70" t="n"/>
+      <c r="H9" s="82" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="70" t="n"/>
+      <c r="J9" s="70" t="n"/>
+      <c r="K9" s="84" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="70" t="n"/>
+      <c r="M9" s="70" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="60" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="85" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="60" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="47" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="48" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="59" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="86" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="48" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="48" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="48" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="48" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="48" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="48" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="49" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="50" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="50" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="51">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="52">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="50" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="53" t="n">
+      <c r="C14" s="86" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="86" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="86" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="87" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="87" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="87" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="87" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="87" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="59" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="59" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="59" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="88" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="88" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="89" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="90" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="74" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="59" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="59" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="59" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="88" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="88" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="89" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="90" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="71" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="59" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="59" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="59" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="59" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="88" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="88" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="89" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="90" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="91" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="59" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="59" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="59" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="59" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="88" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="88" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="89" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="90" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="74" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="59" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="59" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="92" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="93" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="94" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="95" t="inlineStr"/>
+      <c r="L19" s="96" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="59" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="59" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="54" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="49" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="50" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="50" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="51">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="52">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="50" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="53" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="54" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="49" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="50" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="50" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="51">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="52">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="50" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="53" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="54" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="49" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="50" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="50" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="51">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="52">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="50" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="53" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="54" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="49" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="50" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="50" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="51">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="52">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="50" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="53" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="54" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="49" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="50" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="50" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="51">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="52">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="50" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="53" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="54" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="59" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="59" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="97" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="97" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="98" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="99" t="n"/>
+      <c r="M22" s="99" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="59" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="100" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="101" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="99" t="n"/>
+      <c r="M23" s="99" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="59" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="100" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="102" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="103" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="44" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="104" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="105" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="106" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000B3D2E"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ALARMLAR — GES Üretim &amp; Performans Takibi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Alarm listesi — varlık + eşik + süre (S05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Varlık</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Alarm</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>Eşik</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>Süre / Tarih</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>PR Ort</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="inlineStr">
-        <is>
-          <t>Sağlık Skor</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>GES-00001</t>
-        </is>
-      </c>
-      <c r="B6" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A6,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C6" s="24">
-        <f>IFERROR(ABS(E6-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="63">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E6" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>GES-00002</t>
-        </is>
-      </c>
-      <c r="B7" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A7,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C7" s="24">
-        <f>IFERROR(ABS(E7-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="63">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E7" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>GES-00003</t>
-        </is>
-      </c>
-      <c r="B8" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A8,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C8" s="24">
-        <f>IFERROR(ABS(E8-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="63">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E8" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>GES-00004</t>
-        </is>
-      </c>
-      <c r="B9" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A9,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C9" s="24">
-        <f>IFERROR(ABS(E9-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="63">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E9" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>GES-00005</t>
-        </is>
-      </c>
-      <c r="B10" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A10,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C10" s="24">
-        <f>IFERROR(ABS(E10-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="63">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E10" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>GES-00006</t>
-        </is>
-      </c>
-      <c r="B11" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A11,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C11" s="24">
-        <f>IFERROR(ABS(E11-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="63">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E11" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>GES-00007</t>
-        </is>
-      </c>
-      <c r="B12" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A12,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C12" s="24">
-        <f>IFERROR(ABS(E12-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="63">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E12" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>GES-00008</t>
-        </is>
-      </c>
-      <c r="B13" s="7">
-        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A13,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
-        <v/>
-      </c>
-      <c r="C13" s="24">
-        <f>IFERROR(ABS(E13-gup_esikPr),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="63">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-      <c r="E13" s="24">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[OrtPr]),0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="23">
-        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[SaglikSkor]),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Alarm Özeti</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>gup_alarmListesi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Toplam Alarm Satır</t>
-        </is>
-      </c>
-      <c r="B18" s="23">
-        <f>COUNTIF(B6:B13,"ALARM")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A1:N1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6:B13">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
-      <formula>"ALARM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
-      <formula>"YOK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
-    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="0">
-      <formula>gup_esikPr</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="2">
-      <formula>gup_esikSaglik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="8">
-    <dataValidation sqref="A6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="A13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
-      <formula1>1</formula1>
-      <formula2>40</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -22155,7 +21623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -22372,7 +21840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -23032,7 +22500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -23160,7 +22628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -24622,7 +24090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
@@ -24736,241 +24204,473 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G11"/>
+  <dimension ref="B3:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="55" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="B3" s="107" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="108" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="109" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="B5" s="56" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="56" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="56" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="56" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="56" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="56" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
+      <c r="B5" s="110" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="110" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="110" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="110" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="110" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="110" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="110" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="110" t="inlineStr">
+        <is>
+          <t>DURUM</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="57" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="58" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="49" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="59" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
+      <c r="B6" s="111" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="112" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="113" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="114" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="115" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="116">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="113" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="117" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="57" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="58" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="49" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="59" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
+      <c r="B7" s="118" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="119" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="120" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="121" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="123">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="120" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="124" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="57" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="58" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="49" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="59" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="113" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="114" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="116">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="113" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="117" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="57" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="58" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="49" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="59" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
+      <c r="B9" s="118" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="119" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="120" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="121" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="123">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="120" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="125" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="57" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="58" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="49" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="59" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
+      <c r="B10" s="111" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="112" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="113" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="114" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="115" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="116">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="113" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="117" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="57" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="58" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="59" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
+      <c r="B11" s="118" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="119" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="120" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="121" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="123">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="120" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="126" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="111" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="112" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="113" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="114" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="115" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="116">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="113" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="117" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="118" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="119" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="120" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="121" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="123">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="120" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="125" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="111" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="112" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="113" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="114" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="115" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="116">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="113" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="117" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="118" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="119" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="120" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="121" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="123">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="120" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="125" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="127" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="95" t="n"/>
+      <c r="D17" s="95" t="n"/>
+      <c r="E17" s="128">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="95" t="n"/>
+      <c r="G17" s="95" t="n"/>
+      <c r="H17" s="95" t="n"/>
+      <c r="I17" s="95" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24982,81 +24682,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="55" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="60" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="129" t="inlineStr">
+        <is>
+          <t>GES URETIM PERFORMANS — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="130" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="131" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="61" t="inlineStr">
-        <is>
-          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="132" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="70" t="n"/>
+      <c r="D6" s="70" t="n"/>
+      <c r="E6" s="70" t="n"/>
+      <c r="F6" s="70" t="n"/>
+      <c r="H6" s="133" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="70" t="n"/>
+      <c r="J6" s="70" t="n"/>
+      <c r="K6" s="70" t="n"/>
+      <c r="L6" s="70" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="70" t="n"/>
+      <c r="C7" s="70" t="n"/>
+      <c r="D7" s="70" t="n"/>
+      <c r="E7" s="70" t="n"/>
+      <c r="F7" s="70" t="n"/>
+      <c r="H7" s="70" t="n"/>
+      <c r="I7" s="70" t="n"/>
+      <c r="J7" s="70" t="n"/>
+      <c r="K7" s="70" t="n"/>
+      <c r="L7" s="70" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="134" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="70" t="n"/>
+      <c r="D8" s="70" t="n"/>
+      <c r="E8" s="135" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="70" t="n"/>
+      <c r="H8" s="134" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="70" t="n"/>
+      <c r="J8" s="70" t="n"/>
+      <c r="K8" s="136" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="70" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="60" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="134" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="70" t="n"/>
+      <c r="D9" s="70" t="n"/>
+      <c r="E9" s="137" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="70" t="n"/>
+      <c r="H9" s="134" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="70" t="n"/>
+      <c r="J9" s="70" t="n"/>
+      <c r="K9" s="137" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="70" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="61" t="inlineStr">
-        <is>
-          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="134" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="70" t="n"/>
+      <c r="D10" s="70" t="n"/>
+      <c r="E10" s="138" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="70" t="n"/>
+      <c r="H10" s="134" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="70" t="n"/>
+      <c r="J10" s="70" t="n"/>
+      <c r="K10" s="138" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="70" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="134" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="70" t="n"/>
+      <c r="D11" s="70" t="n"/>
+      <c r="E11" s="138" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="70" t="n"/>
+      <c r="H11" s="134" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="70" t="n"/>
+      <c r="J11" s="70" t="n"/>
+      <c r="K11" s="138" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="70" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="70" t="n"/>
+      <c r="C12" s="70" t="n"/>
+      <c r="D12" s="70" t="n"/>
+      <c r="E12" s="70" t="n"/>
+      <c r="F12" s="70" t="n"/>
+      <c r="H12" s="70" t="n"/>
+      <c r="I12" s="70" t="n"/>
+      <c r="J12" s="70" t="n"/>
+      <c r="K12" s="70" t="n"/>
+      <c r="L12" s="70" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="60" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="70" t="n"/>
+      <c r="C13" s="70" t="n"/>
+      <c r="D13" s="70" t="n"/>
+      <c r="E13" s="70" t="n"/>
+      <c r="F13" s="70" t="n"/>
+      <c r="H13" s="70" t="n"/>
+      <c r="I13" s="70" t="n"/>
+      <c r="J13" s="70" t="n"/>
+      <c r="K13" s="70" t="n"/>
+      <c r="L13" s="70" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="139" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="70" t="n"/>
+      <c r="D14" s="70" t="n"/>
+      <c r="E14" s="70" t="n"/>
+      <c r="F14" s="70" t="n"/>
+      <c r="H14" s="140" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="57" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="57" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="70" t="n"/>
+      <c r="C15" s="70" t="n"/>
+      <c r="D15" s="70" t="n"/>
+      <c r="E15" s="70" t="n"/>
+      <c r="F15" s="70" t="n"/>
+      <c r="H15" s="70" t="n"/>
+      <c r="I15" s="70" t="n"/>
+      <c r="J15" s="70" t="n"/>
+      <c r="K15" s="70" t="n"/>
+      <c r="L15" s="70" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="97" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="97" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="97" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="97" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46050,556 +45982,432 @@
   <sheetPr>
     <tabColor rgb="000B3D2E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PANO — GES Üretim &amp; Performans Takibi</t>
+          <t>ALARMLAR — GES Üretim &amp; Performans Takibi</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Karar panosu — PR, kayıp, alarm, sezonsal trend</t>
+          <t>Alarm listesi — varlık + eşik + süre (S05)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>KARAR</t>
-        </is>
-      </c>
-      <c r="B5" s="28">
-        <f>gup_kararKapi</f>
-        <v/>
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Varlık</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Eşik</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Süre / Tarih</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>PR Ort</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>Sağlık Skor</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>Gösterge</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>GES-00001</t>
+        </is>
+      </c>
+      <c r="B6" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A6,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C6" s="24">
+        <f>IFERROR(ABS(E6-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E6" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A6,tblVarliklar[SaglikSkor]),0)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Dolu Kayıt</t>
-        </is>
-      </c>
-      <c r="B7" s="29">
-        <f>gup_doluKayit</f>
-        <v/>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="E7" s="8">
-        <f>gup_kararGerekce</f>
+          <t>GES-00002</t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A7,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C7" s="24">
+        <f>IFERROR(ABS(E7-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E7" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A7,tblVarliklar[SaglikSkor]),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Toplam Üretim kWh</t>
-        </is>
-      </c>
-      <c r="B8" s="30">
-        <f>gup_toplamUretim</f>
+          <t>GES-00003</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A8,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C8" s="24">
+        <f>IFERROR(ABS(E8-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A8,tblVarliklar[SaglikSkor]),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Toplam Kayıp kWh</t>
-        </is>
-      </c>
-      <c r="B9" s="30">
-        <f>gup_toplamKayip</f>
+          <t>GES-00004</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A9,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C9" s="24">
+        <f>IFERROR(ABS(E9-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A9,tblVarliklar[SaglikSkor]),0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>PR Oranı</t>
-        </is>
-      </c>
-      <c r="B10" s="31">
-        <f>gup_prOrani</f>
-        <v/>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Öneri 1</t>
-        </is>
-      </c>
-      <c r="E10" s="8">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"PR",TEXT(gup_prOrani,"0.0%"),"— eşik",TEXT(gup_esikPr,"0.0%"))</f>
+          <t>GES-00005</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A10,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C10" s="24">
+        <f>IFERROR(ABS(E10-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A10,tblVarliklar[SaglikSkor]),0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Teorik Üretim</t>
-        </is>
-      </c>
-      <c r="B11" s="30">
-        <f>gup_teorikUretim</f>
-        <v/>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Öneri 2</t>
-        </is>
-      </c>
-      <c r="E11" s="8">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Alarm",gup_alarmAdet,"adet — sağlık",TEXT(gup_saglikSkor,"0"))</f>
+          <t>GES-00006</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A11,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C11" s="24">
+        <f>IFERROR(ABS(E11-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A11,tblVarliklar[SaglikSkor]),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Kayıp Payı</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
-        <f>gup_kayipPay</f>
-        <v/>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Öneri 3</t>
-        </is>
-      </c>
-      <c r="E12" s="8">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Kayıp",TEXT(gup_toplamKayip,"0"),"kWh — kırılım",gup_kayipKirilim)</f>
+          <t>GES-00007</t>
+        </is>
+      </c>
+      <c r="B12" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A12,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>IFERROR(ABS(E12-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A12,tblVarliklar[SaglikSkor]),0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Günlük PR Ort</t>
-        </is>
-      </c>
-      <c r="B13" s="31">
-        <f>gup_gunlukPrOrt</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Sağlık Skor Ort</t>
-        </is>
-      </c>
-      <c r="B14" s="29">
-        <f>gup_saglikSkor</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Alarm Adet</t>
-        </is>
-      </c>
-      <c r="B15" s="29">
-        <f>gup_alarmAdet</f>
+          <t>GES-00008</t>
+        </is>
+      </c>
+      <c r="B13" s="7">
+        <f>IF(OR(COUNTIFS(tblGunluk[VarlikId],A13,tblGunluk[AlarmBayrak],"ALARM")&gt;0,IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[SaglikSkor]),100)&lt;gup_esikSaglik),"ALARM","YOK")</f>
+        <v/>
+      </c>
+      <c r="C13" s="24">
+        <f>IFERROR(ABS(E13-gup_esikPr),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="63">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[OrtPr]),0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="23">
+        <f>IFERROR(SUMIF(tblVarliklar[VarlikId],A13,tblVarliklar[SaglikSkor]),0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Yetim Kayıt</t>
-        </is>
-      </c>
-      <c r="B16" s="29">
-        <f>gup_yetimAdet</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Kalite Skor</t>
-        </is>
-      </c>
-      <c r="B17" s="29">
-        <f>gup_kaliteSkor</f>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Alarm Özeti</t>
+        </is>
+      </c>
+      <c r="B16" s="8">
+        <f>gup_alarmListesi</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Tornado Zirve</t>
-        </is>
-      </c>
-      <c r="B18" s="30">
-        <f>gup_tornadoZirve</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>P90 Üretim</t>
-        </is>
-      </c>
-      <c r="B19" s="30">
-        <f>gup_yuzdelikP90</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Kayıp Kırılım</t>
-        </is>
-      </c>
-      <c r="B20" s="13">
-        <f>gup_kayipKirilim</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>KayipTuru</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Uretim</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Hafta</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Uretim</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Ay</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>KIRLENME</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Temkinli</t>
-        </is>
-      </c>
-      <c r="E23" s="26" t="n">
-        <v>42000</v>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="H23" s="26" t="n">
-        <v>1280</v>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Haziran</t>
-        </is>
-      </c>
-      <c r="K23" s="24" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>GOLGE</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="n">
-        <v>48000</v>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="H24" s="26" t="n">
-        <v>1360</v>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Temmuz</t>
-        </is>
-      </c>
-      <c r="K24" s="24" t="n">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>INVERTER</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="E25" s="26" t="n">
-        <v>54000</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="H25" s="26" t="n">
-        <v>1440</v>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Agustos</t>
-        </is>
-      </c>
-      <c r="K25" s="24" t="n">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>ARIZA</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="H26" s="26" t="n">
-        <v>1520</v>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>Eylul</t>
-        </is>
-      </c>
-      <c r="K26" s="24" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="H27" s="26" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>H6</t>
-        </is>
-      </c>
-      <c r="H28" s="26" t="n">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="H29" s="26" t="n">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>H8</t>
-        </is>
-      </c>
-      <c r="H30" s="26" t="n">
-        <v>1840</v>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Toplam Alarm Satır</t>
+        </is>
+      </c>
+      <c r="B18" s="23">
+        <f>COUNTIF(B6:B13,"ALARM")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="E7:H8"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
-      <formula>"UYGUN"</formula>
+  <conditionalFormatting sqref="B6:B13">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
+      <formula>"ALARM"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
-      <formula>"DİKKAT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
-      <formula>"KRİTİK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
-      <formula>"VERİ YOK"</formula>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
+      <formula>"YOK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="cellIs" priority="10" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
-    <cfRule type="cellIs" priority="14" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
-    <cfRule type="cellIs" priority="16" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
-    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="E12">
+    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="cellIs" priority="18" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LGES Üretim &amp; Performans Takibi | Pano | 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LGES Üretim &amp; Performans Takibi | Pano | 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="0">
+      <formula>gup_esikPr</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="2">
+      <formula>gup_esikSaglik</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation sqref="A6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+    <dataValidation sqref="A13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Varlık" error="Boş olamaz" promptTitle="Varlık" prompt="Varlık kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
+      <formula1>1</formula1>
+      <formula2>40</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>